--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_Inputs_BRD-02_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_Inputs_BRD-02_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Start here'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Documents and print formats'!$A$12:$K$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Documents and print formats'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'E-mail wordings'!$A$12:$K$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'E-mail wordings'!$A$12:$K$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'E-mail wordings'!$12:$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Messages to confirm'!$A$12:$K$144</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Messages to confirm'!$12:$12</definedName>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>18 items</t>
+          <t>19 items</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
@@ -9102,7 +9102,7 @@
         </is>
       </c>
       <c r="F6" s="24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6" s="24">
         <f>COUNTIF('E-mail wordings'!K:K,"Open")</f>
@@ -11687,7 +11687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12862,7 +12862,7 @@
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>AR / OR creation record for posting</t>
+          <t>AR / OR record for posting</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>Approve the wording, the trigger and the recipients. Trigger: An AR or OR creation record is submitted for posting (BDOI FRS.CSH.02.01.10). Recipients: The Approver / Poster of the branch (Head Office for ORs). Subject: &lt;record number&gt; for posting. Text: &lt;Acknowledgement / Official Receipt&gt; &lt;type&gt;, &lt;payor&gt;, &lt;currency&gt; &lt;amount&gt;</t>
+          <t>Approve the wording, the trigger and the recipients. Trigger: An AR or OR creation, cancellation or reinstatement record is submitted for posting (BDOI FRS.CSH.02.01.10). Recipients: Every holder of the posting right (Cashiering Team Leaders and Team Heads). Subject: &lt;record number&gt; for posting. Text: &lt;record type&gt; of &lt;amount&gt; waits for posting</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>AR / OR creation record returned or posted</t>
+          <t>AR / OR record posted or returned</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>Approve the wording, the trigger and the recipients. Trigger: The Approver / Poster returns or posts an AR or OR creation record. Recipients: The creator of the record. Subject: &lt;record number&gt; returned / &lt;record number&gt; posted: &lt;AR / OR number&gt;. Text: Returned: &lt;reason&gt;. Posted: &lt;AR / OR number&gt; issued and applied to &lt;n&gt; account(s).</t>
+          <t>Approve the wording, the trigger and the recipients. Trigger: The Approver / Poster posts or returns an AR or OR record. Recipients: The creator of the record. Subject: &lt;record number&gt; posted / &lt;record number&gt; returned. Text: Posted: &lt;record type&gt;: &lt;AR / OR&gt; &lt;number&gt;. Returned: Reason: &lt;reason&gt;.</t>
         </is>
       </c>
       <c r="F29" s="24" t="inlineStr">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>Approve the wording, the trigger and the recipients. Trigger: A payment file received via MFT fails the file checks (FRS.CSH.05.01.04). Recipients: Cashiering Team Leader (alert inbox). Subject: Payment file &lt;file name&gt; refused: &lt;reason&gt;. Text: The file and its validation report.</t>
+          <t>Approve the wording, the trigger and the recipients. Trigger: A payment file received via MFT fails the file checks (FRS.CSH.05.01.04). Recipients: Cashiering Team Leader (alert inbox). Subject: Payment file &lt;file name&gt; received via MFT was refused: &lt;reason&gt;. Text: The file with its reason; the file is kept in the refused folder.</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -13016,47 +13016,47 @@
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>RC-EML-18</t>
+          <t>G-18</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Sender and footer of the e-mails</t>
+          <t>AR or OR form change for approval</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>BRQID.005</t>
+          <t>CSHID.019</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>Appendix G</t>
+          <t>Appendix G; FRS.CSH.02.06.01</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
         <is>
-          <t>The sender address of each environment and, if required, the standard footer or disclaimer of BDOI e-mails.</t>
+          <t>Approve the wording, the trigger and the recipients. Trigger: A new version of the AR or OR form is saved (FRS.CSH.02.06.01). Recipients: Every holder of the master data approval right, except the user who changed the form. Subject: &lt;AR / OR&gt; form version &lt;number&gt; for approval. Text: Effective &lt;date&gt;, changed by &lt;user&gt;</t>
         </is>
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>Address per environment; footer text</t>
+          <t>Approve, or the new wording</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
         <is>
-          <t>bibs-noreply@ (domain of BDOI)</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr">
         <is>
-          <t>BDOI IT</t>
+          <t>Cashiering Process Owner</t>
         </is>
       </c>
       <c r="I31" s="24" t="inlineStr">
         <is>
-          <t>16-Jul-2027</t>
+          <t>30-Nov-2026</t>
         </is>
       </c>
       <c r="J31" s="24" t="inlineStr"/>
@@ -13066,8 +13066,61 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>RC-EML-19</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Sender and footer of the e-mails</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>BRQID.005</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>Appendix G</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>The sender address of each environment and, if required, the standard footer or disclaimer of BDOI e-mails.</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>Address per environment; footer text</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>bibs-noreply@ (domain of BDOI)</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>BDOI IT</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J32" s="22" t="inlineStr"/>
+      <c r="K32" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A12:K31"/>
+  <autoFilter ref="A12:K32"/>
   <mergeCells count="5">
     <mergeCell ref="B4:K4"/>
     <mergeCell ref="B6:K6"/>
@@ -13076,7 +13129,7 @@
     <mergeCell ref="B5:K5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K14:K331" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="K14:K332" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_Inputs_BRD-02_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_Inputs_BRD-02_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -43,7 +43,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Master and reference data'!$12:$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Approvers and users per role'!$A$12:$K$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'Approvers and users per role'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Integration inputs'!$A$12:$K$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Integration inputs'!$A$12:$K$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'Integration inputs'!$12:$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Open decisions'!$A$12:$K$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Open decisions'!$12:$12</definedName>
@@ -819,7 +819,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>10 October 2026</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D30" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
@@ -3729,7 +3729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="E13" s="30" t="inlineStr">
         <is>
-          <t>MFT folder, arrival time, positions 7 to 13 of the layout (exchanged: Bills Payment file BDOIYYYYMMDD.txt (Appendix D.1); Daily, via MFT). Status of BDOI's input: Given in part (sample, file name).</t>
+          <t>MFT folder, arrival time, positions 7 to 13 of the layout (exchanged: Bills Payment file BDOIYYYYMMDD.txt with its header record (Appendix D.1); Daily, via MFT, taken at the times set and on Receive MFT Files Now). Status of BDOI's input: Given in part (sample, file name). Available in BIBS: intake with the name, size, duplicate and header checks, run report, refusal alert and processing again; run end to end in SIT and UAT against the channel simulator. Connection details from BDOI IT at SIT.</t>
         </is>
       </c>
       <c r="F13" s="30" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>MFT folder, arrival time, positions 7 to 13 of the layout (exchanged: Bills Payment file BDOIYYYYMMDD.txt (Appendix D.1); Daily, via MFT). Status of BDOI's input: Given in part (sample, file name).</t>
+          <t>MFT folder, arrival time, positions 7 to 13 of the layout (exchanged: Bills Payment file BDOIYYYYMMDD.txt with its header record (Appendix D.1); Daily, via MFT, taken at the times set and on Receive MFT Files Now). Status of BDOI's input: Given in part (sample, file name). Available in BIBS: intake with the name, size, duplicate and header checks, run report, refusal alert and processing again; run end to end in SIT and UAT against the channel simulator. Connection details from BDOI IT at SIT.</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>MFT folder, time, the header and detail layout (exchanged: Matured post-dated checks BDOIYYYYMMDDPMS.txt (Appendix D.2); Daily, via MFT). Status of BDOI's input: To be provided.</t>
+          <t>MFT folder, time, the header and detail layout (exchanged: Matured post-dated checks BDOIYYYYMMDDPMS.txt (Appendix D.2); Daily, via MFT). Status of BDOI's input: To be provided. Available in BIBS in the proposed layout and run end to end against the channel simulator; layout and folder from BDOI IT at SIT.</t>
         </is>
       </c>
       <c r="F15" s="24" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>Separator of the file (exchanged: Trade file UploadTrade_MM.DD.YYYY.txt (Appendix D.4); Daily, upload by the Cashier). Status of BDOI's input: Given in part (sample).</t>
+          <t>Separator of the file (exchanged: Trade file UploadTrade_MM.DD.YYYY.txt (Appendix D.4); Daily, upload by the Cashier (several files in one upload)). Status of BDOI's input: Given in part (sample). Available in BIBS; the channel simulator writes the file for SIT and UAT.</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>Layout of the file (exchanged: Direct Credit file OTCYYYYMMDD-&lt;branch&gt;.txt (Appendix D.5); Daily, upload). Status of BDOI's input: To be provided.</t>
+          <t>Layout of the file (exchanged: Direct Credit file OTCYYYYMMDD-&lt;branch&gt;.txt (Appendix D.5) identifying the payments of a Bills Payment file (setting, Appendix H.8); Daily, upload). Status of BDOI's input: To be provided. Available in BIBS in the proposed layout; the channel simulator writes the file for SIT and UAT.</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>- (exchanged: CLPC file CLPC-MonDDYYYY.xlsx (Appendix D.3); Daily, upload). Status of BDOI's input: Given (sample).</t>
+          <t>- (exchanged: CLPC file CLPC-MonDDYYYY.xlsx with its TOTAL row (Appendix D.3); Daily, upload). Status of BDOI's input: Given (sample). Available in BIBS; the channel simulator writes the file for SIT and UAT.</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>BIBS New Business</t>
+          <t>Insurers (Commission Schedule)</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>- (exchanged: Booked accounts with their components (in); payment confirmation of each account (out); At booking; at each payment). Status of BDOI's input: Not needed.</t>
+          <t>- (exchanged: Commission Schedule of the commission paid by an insurer, matched to the commission receivable of each account; At each insurer payment, upload). Status of BDOI's input: Layout proposed in BIBS (Appendix D); valid lines processed as delivered (setting, Appendix H.8).</t>
         </is>
       </c>
       <c r="F19" s="24" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H19" s="24" t="inlineStr">
         <is>
-          <t>New Business</t>
+          <t>Commission Receivables</t>
         </is>
       </c>
       <c r="I19" s="24" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>BIBS Collections</t>
+          <t>Channel simulator (SIT and UAT only)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>- (exchanged: Collector requests on unapplied payments; commission payment details; their result; At each request). Status of BDOI's input: Not needed.</t>
+          <t>- (exchanged: Payment files of every type in BDOI's layouts for booked accounts, one account not yet booked and one unknown reference, dropped in the MFT folders or handed for upload; On request of the test lead). Status of BDOI's input: Not used in production; it cannot run outside SIT and UAT.</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="H20" s="22" t="inlineStr">
         <is>
-          <t>Collections</t>
+          <t>iorta TechNXT Project Team</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>BIBS Disbursement</t>
+          <t>BIBS New Business</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>- (exchanged: Refund requests (out); their status and the approved insurer settlements that trigger the automatic OR (in); At approval; at each status). Status of BDOI's input: Not needed.</t>
+          <t>- (exchanged: Booked accounts with their components (in); payment confirmation of each account (out); At booking; at each payment). Status of BDOI's input: Not needed.</t>
         </is>
       </c>
       <c r="F21" s="24" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="H21" s="24" t="inlineStr">
         <is>
-          <t>Disbursement</t>
+          <t>New Business</t>
         </is>
       </c>
       <c r="I21" s="24" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>BIBS Remittance</t>
+          <t>BIBS Collections</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>- (exchanged: Paid and applied premium of each account (out); remittance status (in); At each application; at each remittance). Status of BDOI's input: Not needed.</t>
+          <t>- (exchanged: Collector requests on unapplied payments; commission payment details; their result; At each request). Status of BDOI's input: Not needed.</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="H22" s="22" t="inlineStr">
         <is>
-          <t>Remittance</t>
+          <t>Collections</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>BIBS Accounting</t>
+          <t>BIBS Disbursement</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>- (exchanged: The journal of every posting (out); the exchange rates and the accounts of the entries (in); At each posting; daily rates). Status of BDOI's input: Accounts to be given (Appendix S).</t>
+          <t>- (exchanged: Refund requests (out); their status and the approved insurer settlements that trigger the automatic OR (in); At approval; at each status). Status of BDOI's input: Not needed.</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="H23" s="24" t="inlineStr">
         <is>
-          <t>Comptrollership</t>
+          <t>Disbursement</t>
         </is>
       </c>
       <c r="I23" s="24" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>Marketing Collection / Commission Receivable</t>
+          <t>BIBS Remittance</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>- (exchanged: Unapplied records of their units; AP Unapplied Commission; PR 2307 kept outstanding; At each record). Status of BDOI's input: Owner of MKTID.013 to confirm (Appendix R).</t>
+          <t>- (exchanged: Paid and applied premium of each account (out); remittance status (in); At each application; at each remittance). Status of BDOI's input: Not needed.</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="H24" s="22" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Remittance</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>BRD-13 Data Migration</t>
+          <t>BIBS Accounting</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>Extracts of the legacy systems (exchanged: Open accounts with legacy numbers, unapplied payments, post-dated checks, receipt series in use (Appendix P); Trial migrations and go-live). Status of BDOI's input: Per the drop plan.</t>
+          <t>- (exchanged: The journal of every posting (out); the exchange rates and the accounts of the entries (in); At each posting; daily rates). Status of BDOI's input: Accounts to be given (Appendix S).</t>
         </is>
       </c>
       <c r="F25" s="24" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="H25" s="24" t="inlineStr">
         <is>
-          <t>Data Migration lead</t>
+          <t>Comptrollership</t>
         </is>
       </c>
       <c r="I25" s="24" t="inlineStr">
@@ -4793,47 +4793,47 @@
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>CFG-044</t>
+          <t>RC-INT-13</t>
         </is>
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>Payment file layouts of the collection channels</t>
+          <t>Marketing Collection / Commission Receivable</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
         <is>
-          <t>CSHID.008</t>
+          <t>BRQID.004, 005</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
         <is>
-          <t>FRS.CSH.05.01.06; Appendix D</t>
+          <t>Appendix N</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
         <is>
-          <t>Payment file layouts of the collection channels: Confirmation of the payment files received from Bills Payment, Trade, Direct Credit, CLPC and PMS and their field names</t>
+          <t>- (exchanged: Unapplied records of their units; AP Unapplied Commission; PR 2307 kept outstanding; At each record). Status of BDOI's input: Owner of MKTID.013 to confirm (Appendix R).</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t>Layout per channel (field, position, format)</t>
+          <t>Details, or Confirm</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
         <is>
-          <t>Layout of the PMS file</t>
+          <t>Folder, time and layout</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
         <is>
-          <t>Operations Head</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
         <is>
-          <t>16-Jul-2027</t>
+          <t>31-Jan-2027</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr"/>
@@ -4846,43 +4846,47 @@
     <row r="27">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>D-OP-01</t>
+          <t>RC-INT-14</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Dependency</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr"/>
+          <t>BRD-13 Data Migration</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>BRQID.004, 005</t>
+        </is>
+      </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>Appendix S.2; FRS.CSH.05.01.06; Appendix D</t>
+          <t>Appendix N</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>BDOI gives the layouts of the channel files not yet given (PMS, Direct Credit, Commission Schedule, positions of the Bills Payment file).</t>
+          <t>Extracts of the legacy systems (exchanged: Open accounts with legacy numbers, unapplied payments, post-dated checks, receipt series in use (Appendix P); Trial migrations and go-live). Status of BDOI's input: Per the drop plan.</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>Date when it is in place</t>
+          <t>Details, or Confirm</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
         <is>
-          <t>09-Apr-2027</t>
+          <t>Folder, time and layout</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
         <is>
-          <t>BDOI IT</t>
+          <t>Data Migration lead</t>
         </is>
       </c>
       <c r="I27" s="24" t="inlineStr">
         <is>
-          <t>09-Apr-2027</t>
+          <t>31-Jan-2027</t>
         </is>
       </c>
       <c r="J27" s="24" t="inlineStr"/>
@@ -4895,43 +4899,47 @@
     <row r="28">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>D-OP-02</t>
+          <t>CFG-044</t>
         </is>
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>Dependency</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr"/>
+          <t>Payment file layouts of the collection channels</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>CSHID.008</t>
+        </is>
+      </c>
       <c r="D28" s="22" t="inlineStr">
         <is>
-          <t>Appendix S.2; FRS.CSH.02.03</t>
+          <t>FRS.CSH.05.01.06; Appendix D</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>BDOI gives the BIR-registered AR and OR series and formats (ATP).</t>
+          <t>Payment file layouts of the collection channels: Confirmation of the payment files received from Bills Payment, Trade, Direct Credit, CLPC and PMS and their field names</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t>Date when it is in place</t>
+          <t>Layout per channel (field, position, format)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
         <is>
-          <t>09-Apr-2027</t>
+          <t>Layout of the PMS file</t>
         </is>
       </c>
       <c r="H28" s="22" t="inlineStr">
         <is>
-          <t>Cashiering Process Owner</t>
+          <t>Operations Head</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
         <is>
-          <t>09-Apr-2027</t>
+          <t>16-Jul-2027</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr"/>
@@ -4944,7 +4952,7 @@
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>D-OP-03</t>
+          <t>D-OP-01</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
@@ -4955,12 +4963,12 @@
       <c r="C29" s="24" t="inlineStr"/>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>Appendix S.2; Appendix I</t>
+          <t>Appendix S.2; FRS.CSH.05.01.06; Appendix D</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>Comptrollership gives the GL accounts of the entries and the source of the exchange rate.</t>
+          <t>BDOI gives the layouts of the channel files not yet given (PMS, Direct Credit, Commission Schedule, positions of the Bills Payment file).</t>
         </is>
       </c>
       <c r="F29" s="24" t="inlineStr">
@@ -4975,7 +4983,7 @@
       </c>
       <c r="H29" s="24" t="inlineStr">
         <is>
-          <t>Cashiering Process Owner</t>
+          <t>BDOI IT</t>
         </is>
       </c>
       <c r="I29" s="24" t="inlineStr">
@@ -4993,7 +5001,7 @@
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>D-OP-04</t>
+          <t>D-OP-02</t>
         </is>
       </c>
       <c r="B30" s="22" t="inlineStr">
@@ -5004,12 +5012,12 @@
       <c r="C30" s="22" t="inlineStr"/>
       <c r="D30" s="22" t="inlineStr">
         <is>
-          <t>Appendix S.2; FRS.CSH.06.03, 07.01, 10.01</t>
+          <t>Appendix S.2; FRS.CSH.02.03</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>The BIBS Collections and Disbursement modules (BRD-4, BRD-5) are in use for the requests, refunds and settlements.</t>
+          <t>BDOI gives the BIR-registered AR and OR series and formats (ATP).</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -5042,7 +5050,7 @@
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>D-OP-07</t>
+          <t>D-OP-03</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
@@ -5053,12 +5061,12 @@
       <c r="C31" s="24" t="inlineStr"/>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>Appendix S.2; Appendix G</t>
+          <t>Appendix S.2; Appendix I</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
         <is>
-          <t>The e-mail relay of the BIBS environment is available for the failed-run e-mail.</t>
+          <t>Comptrollership gives the GL accounts of the entries and the source of the exchange rate.</t>
         </is>
       </c>
       <c r="F31" s="24" t="inlineStr">
@@ -5073,7 +5081,7 @@
       </c>
       <c r="H31" s="24" t="inlineStr">
         <is>
-          <t>BDOI IT</t>
+          <t>Cashiering Process Owner</t>
         </is>
       </c>
       <c r="I31" s="24" t="inlineStr">
@@ -5091,43 +5099,43 @@
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
         <is>
-          <t>OQ03</t>
+          <t>D-OP-04</t>
         </is>
       </c>
       <c r="B32" s="22" t="inlineStr">
         <is>
-          <t>Give the layouts not in BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="inlineStr">
-        <is>
-          <t>CSHID.008</t>
-        </is>
-      </c>
+          <t>Dependency</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr"/>
       <c r="D32" s="22" t="inlineStr">
         <is>
-          <t>Appendix S.3.2 (OQ03)</t>
+          <t>Appendix S.2; FRS.CSH.06.03, 07.01, 10.01</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>Give the layouts not in BDOI's FRS: the PMS post-dated check file (header and details), the Direct Credit file, the Commission Schedule fields, and the meaning of positions 7 to 13 of the Bills Payment file.</t>
+          <t>The BIBS Collections and Disbursement modules (BRD-4, BRD-5) are in use for the requests, refunds and settlements.</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t>One real file of each channel and its field list</t>
-        </is>
-      </c>
-      <c r="G32" s="22" t="inlineStr"/>
+          <t>Date when it is in place</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>09-Apr-2027</t>
+        </is>
+      </c>
       <c r="H32" s="22" t="inlineStr">
         <is>
-          <t>Cashiering Process Owner; BDOI IT</t>
+          <t>Cashiering Process Owner</t>
         </is>
       </c>
       <c r="I32" s="22" t="inlineStr">
         <is>
-          <t>31-Jan-2027</t>
+          <t>09-Apr-2027</t>
         </is>
       </c>
       <c r="J32" s="22" t="inlineStr"/>
@@ -5140,35 +5148,35 @@
     <row r="33">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>IQ09</t>
+          <t>D-OP-07</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>MFT of the OBPCS and PMS files</t>
-        </is>
-      </c>
-      <c r="C33" s="24" t="inlineStr">
-        <is>
-          <t>BRQID.005</t>
-        </is>
-      </c>
+          <t>Dependency</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr"/>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>Appendix S.3.3 (IQ09; IQ10)</t>
+          <t>Appendix S.2; Appendix G</t>
         </is>
       </c>
       <c r="E33" s="24" t="inlineStr">
         <is>
-          <t>MFT of the OBPCS and PMS files: folder, arrival times, frequency, what happens when a file is late or missing.</t>
+          <t>The e-mail relay of the BIBS environment is available for the failed-run e-mail.</t>
         </is>
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
-          <t>Folder per environment; times; contact on failure</t>
-        </is>
-      </c>
-      <c r="G33" s="24" t="inlineStr"/>
+          <t>Date when it is in place</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>09-Apr-2027</t>
+        </is>
+      </c>
       <c r="H33" s="24" t="inlineStr">
         <is>
           <t>BDOI IT</t>
@@ -5176,7 +5184,7 @@
       </c>
       <c r="I33" s="24" t="inlineStr">
         <is>
-          <t>31-Jan-2027</t>
+          <t>09-Apr-2027</t>
         </is>
       </c>
       <c r="J33" s="24" t="inlineStr"/>
@@ -5189,43 +5197,43 @@
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>OQ44</t>
+          <t>OQ03</t>
         </is>
       </c>
       <c r="B34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirm the non-functional values of Appendix O for Cashiering </t>
+          <t>Give the layouts not in BDOI's FRS</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
         <is>
-          <t>CSHID.001-025</t>
+          <t>CSHID.008</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
         <is>
-          <t>Appendix S.3.8 (OQ44)</t>
+          <t>Appendix S.3.2 (OQ03)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>Confirm the non-functional values of Appendix O for Cashiering (response time, volumes per day, peak days, file sizes).</t>
+          <t>Give the layouts not in BDOI's FRS: the PMS post-dated check file (header and details), the Direct Credit file, the Commission Schedule fields, and the meaning of positions 7 to 13 of the Bills Payment file.</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t>Value per row of Appendix O</t>
+          <t>One real file of each channel and its field list</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr"/>
       <c r="H34" s="22" t="inlineStr">
         <is>
-          <t>BDOI IT</t>
+          <t>Cashiering Process Owner; BDOI IT</t>
         </is>
       </c>
       <c r="I34" s="22" t="inlineStr">
         <is>
-          <t>01-Dec-2026</t>
+          <t>31-Jan-2027</t>
         </is>
       </c>
       <c r="J34" s="22" t="inlineStr"/>
@@ -5235,8 +5243,106 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>IQ09</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>MFT of the OBPCS and PMS files</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>BRQID.005</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>Appendix S.3.3 (IQ09; IQ10)</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>MFT of the OBPCS and PMS files: folder, arrival times, frequency, what happens when a file is late or missing.</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>Folder per environment; times; contact on failure</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr"/>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>BDOI IT</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>31-Jan-2027</t>
+        </is>
+      </c>
+      <c r="J35" s="24" t="inlineStr"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>OQ44</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm the non-functional values of Appendix O for Cashiering </t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>Appendix S.3.8 (OQ44)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>Confirm the non-functional values of Appendix O for Cashiering (response time, volumes per day, peak days, file sizes).</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>Value per row of Appendix O</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr"/>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>BDOI IT</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>01-Dec-2026</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr"/>
+      <c r="K36" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A12:K34"/>
+  <autoFilter ref="A12:K36"/>
   <mergeCells count="5">
     <mergeCell ref="B4:K4"/>
     <mergeCell ref="B6:K6"/>
@@ -5245,7 +5351,7 @@
     <mergeCell ref="B5:K5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K14:K334" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="K14:K336" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -9382,7 +9488,7 @@
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>21 items</t>
+          <t>23 items</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -9396,7 +9502,7 @@
         </is>
       </c>
       <c r="F13" s="22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G13" s="22">
         <f>COUNTIF('Integration inputs'!K:K,"Open")</f>
@@ -20946,7 +21052,7 @@
       </c>
       <c r="E13" s="30" t="inlineStr">
         <is>
-          <t>Confirm the time (At the times agreed with BDOI IT (proposed: every hour from 07:00 to 18:00)) and who is told: Cashiering Team Leader: alert when a file is refused.</t>
+          <t>Confirm the time (At the times agreed with BDOI IT (proposed: every hour from 07:00 to 18:00), and on Receive MFT Files Now) and who is told: Cashiering Team Leader: alert when a file is refused.</t>
         </is>
       </c>
       <c r="F13" s="30" t="inlineStr">
@@ -20956,7 +21062,7 @@
       </c>
       <c r="G13" s="30" t="inlineStr">
         <is>
-          <t>At the times agreed with BDOI IT (proposed: every hour from 07:00 to 18:00)</t>
+          <t>At the times agreed with BDOI IT (proposed: every hour from 07:00 to 18:00), and on Receive MFT Files Now</t>
         </is>
       </c>
       <c r="H13" s="30" t="inlineStr">
@@ -20971,7 +21077,7 @@
       </c>
       <c r="J13" s="30" t="inlineStr">
         <is>
-          <t>At the times agreed with BDOI IT (proposed: every hour from 07:00 to 18:00)</t>
+          <t>At the times agreed with BDOI IT (proposed: every hour from 07:00 to 18:00), and on Receive MFT Files Now</t>
         </is>
       </c>
       <c r="K13" s="30" t="inlineStr">
@@ -21003,7 +21109,7 @@
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>Confirm the time (At the times agreed with BDOI IT (proposed: every hour from 07:00 to 18:00)) and who is told: Cashiering Team Leader: alert when a file is refused.</t>
+          <t>Confirm the time (At the times agreed with BDOI IT (proposed: every hour from 07:00 to 18:00), and on Receive MFT Files Now) and who is told: Cashiering Team Leader: alert when a file is refused.</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -21013,7 +21119,7 @@
       </c>
       <c r="G14" s="22" t="inlineStr">
         <is>
-          <t>At the times agreed with BDOI IT (proposed: every hour from 07:00 to 18:00)</t>
+          <t>At the times agreed with BDOI IT (proposed: every hour from 07:00 to 18:00), and on Receive MFT Files Now</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_Inputs_BRD-02_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_Inputs_BRD-02_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Documents and print formats'!$12:$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'E-mail wordings'!$A$12:$K$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'E-mail wordings'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Messages to confirm'!$A$12:$K$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Messages to confirm'!$A$12:$K$162</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Messages to confirm'!$12:$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Schedules and timings'!$A$12:$K$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Schedules and timings'!$12:$12</definedName>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>131</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>131 items</t>
+          <t>149 items</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="F7" s="22" t="n">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="G7" s="22">
         <f>COUNTIF('Messages to confirm'!K:K,"Open")</f>
@@ -13259,7 +13259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K144"/>
+  <dimension ref="A1:K162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14111,12 +14111,12 @@
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>M-020</t>
+          <t>M-049</t>
         </is>
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>Receive Payment (SCR-OP-08) and the application of payments</t>
+          <t>AR and OR Forms and printing (SCR-OP-69, SCR-OP-18)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A reclass or transfer moves the whole balance" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The effective date must be today or a later date" (type Error).</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -14164,12 +14164,12 @@
     <row r="23">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>M-021</t>
+          <t>M-050</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Receive Payment (SCR-OP-08) and the application of payments</t>
+          <t>AR and OR Forms and printing (SCR-OP-69, SCR-OP-18)</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Check number is required for a check payment" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Select the AR form or the OR form" (type Error).</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
@@ -14217,12 +14217,12 @@
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>M-022</t>
+          <t>M-051</t>
         </is>
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>Receive Payment (SCR-OP-08) and the application of payments</t>
+          <t>AR and OR Forms and printing (SCR-OP-69, SCR-OP-18)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an ARN, invoice, policy or PN number to preview the application." (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the reason for the rejection" (type Error).</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -14270,7 +14270,7 @@
     <row r="25">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>M-023</t>
+          <t>M-053</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A reclass or transfer moves the whole balance" (type Validation).</t>
         </is>
       </c>
       <c r="F25" s="24" t="inlineStr">
@@ -14323,7 +14323,7 @@
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>M-024</t>
+          <t>M-054</t>
         </is>
       </c>
       <c r="B26" s="22" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="E26" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero and at most &lt;balance&gt;" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Check number is required for a check payment" (type Validation).</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -14376,7 +14376,7 @@
     <row r="27">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>M-025</t>
+          <t>M-055</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero and at most &lt;receipt amount&gt;" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an ARN, invoice, policy or PN number to preview the application." (type Validation).</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">
@@ -14429,7 +14429,7 @@
     <row r="28">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>M-026</t>
+          <t>M-056</t>
         </is>
       </c>
       <c r="B28" s="22" t="inlineStr">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter at least one reference, or the payor code for an unmatched payment" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero" (type Validation).</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -14482,7 +14482,7 @@
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>M-027</t>
+          <t>M-057</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Payor name is required" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero and at most &lt;balance&gt;" (type Validation).</t>
         </is>
       </c>
       <c r="F29" s="24" t="inlineStr">
@@ -14535,7 +14535,7 @@
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>M-028</t>
+          <t>M-058</t>
         </is>
       </c>
       <c r="B30" s="22" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Select a reason" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero and at most &lt;receipt amount&gt;" (type Validation).</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -14588,7 +14588,7 @@
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>M-029</t>
+          <t>M-059</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="E31" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The reference belongs to a cancelled invoice: the payment goes to unapplied collections." (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter at least one reference, or the payor code for an unmatched payment" (type Validation).</t>
         </is>
       </c>
       <c r="F31" s="24" t="inlineStr">
@@ -14641,7 +14641,7 @@
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
         <is>
-          <t>M-030</t>
+          <t>M-060</t>
         </is>
       </c>
       <c r="B32" s="22" t="inlineStr">
@@ -14661,7 +14661,7 @@
       </c>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Application &lt;id&gt; is already reversed" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Payor name is required" (type Validation).</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -14694,7 +14694,7 @@
     <row r="33">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>M-031</t>
+          <t>M-061</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="E33" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A non-premium AR needs the paying insurer's code" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Select a reason" (type Validation).</t>
         </is>
       </c>
       <c r="F33" s="24" t="inlineStr">
@@ -14747,7 +14747,7 @@
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>M-032</t>
+          <t>M-062</t>
         </is>
       </c>
       <c r="B34" s="22" t="inlineStr">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Official receipts are issued by Head Office only" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The reference belongs to a cancelled invoice: the payment goes to unapplied collections." (type Validation).</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -14800,7 +14800,7 @@
     <row r="35">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>M-033</t>
+          <t>M-063</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="E35" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "An official receipt needs a line" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Application &lt;id&gt; is already reversed" (type Error).</t>
         </is>
       </c>
       <c r="F35" s="24" t="inlineStr">
@@ -14853,7 +14853,7 @@
     <row r="36">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>M-034</t>
+          <t>M-064</t>
         </is>
       </c>
       <c r="B36" s="22" t="inlineStr">
@@ -14873,7 +14873,7 @@
       </c>
       <c r="E36" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A receipt needs an amount above zero" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A non-premium AR needs the paying insurer's code" (type Error).</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -14906,12 +14906,12 @@
     <row r="37">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>M-035</t>
+          <t>M-065</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>Receipts, Issue Official Receipt and the receipt series (SCR</t>
+          <t>Receive Payment (SCR-OP-08) and the application of payments</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="E37" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;receipt no&gt; issued" (type Confirmation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Official receipts are issued by Head Office only" (type Error).</t>
         </is>
       </c>
       <c r="F37" s="24" t="inlineStr">
@@ -14959,12 +14959,12 @@
     <row r="38">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>M-036</t>
+          <t>M-066</t>
         </is>
       </c>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>Receipts, Issue Official Receipt and the receipt series (SCR</t>
+          <t>Receive Payment (SCR-OP-08) and the application of payments</t>
         </is>
       </c>
       <c r="C38" s="22" t="inlineStr">
@@ -14979,7 +14979,7 @@
       </c>
       <c r="E38" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the gross amount" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "An official receipt needs a line" (type Error).</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -15012,12 +15012,12 @@
     <row r="39">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>M-037</t>
+          <t>M-067</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>Receipts, Issue Official Receipt and the receipt series (SCR</t>
+          <t>Receive Payment (SCR-OP-08) and the application of payments</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="E39" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Payor name is required" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A receipt needs an amount above zero" (type Error).</t>
         </is>
       </c>
       <c r="F39" s="24" t="inlineStr">
@@ -15065,7 +15065,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>M-038</t>
+          <t>M-068</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
@@ -15085,7 +15085,7 @@
       </c>
       <c r="E40" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Select the OR type" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;receipt no&gt; issued" (type Confirmation).</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
@@ -15118,7 +15118,7 @@
     <row r="41">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>M-039</t>
+          <t>M-069</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="E41" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "VAT and withholding tax cannot be negative" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the gross amount" (type Validation).</t>
         </is>
       </c>
       <c r="F41" s="24" t="inlineStr">
@@ -15171,7 +15171,7 @@
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>M-040</t>
+          <t>M-070</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="E42" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Branch &lt;code&gt; is not of this company" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No receipts match the search" (type Information).</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
@@ -15224,7 +15224,7 @@
     <row r="43">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>M-041</t>
+          <t>M-071</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="E43" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The company has no Head Office branch for official receipts" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Payor name is required" (type Validation).</t>
         </is>
       </c>
       <c r="F43" s="24" t="inlineStr">
@@ -15277,7 +15277,7 @@
     <row r="44">
       <c r="A44" s="22" t="inlineStr">
         <is>
-          <t>M-042</t>
+          <t>M-072</t>
         </is>
       </c>
       <c r="B44" s="22" t="inlineStr">
@@ -15297,7 +15297,7 @@
       </c>
       <c r="E44" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Official receipt series belong to Head Office only" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Select the OR type" (type Validation).</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
@@ -15330,7 +15330,7 @@
     <row r="45">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>M-043</t>
+          <t>M-073</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="E45" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No authorized &lt;kind&gt; series with numbers left for this branch" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "VAT and withholding tax cannot be negative" (type Validation).</t>
         </is>
       </c>
       <c r="F45" s="24" t="inlineStr">
@@ -15383,7 +15383,7 @@
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>M-044</t>
+          <t>M-074</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="E46" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt series &lt;prefix&gt; is depleted" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Branch &lt;code&gt; is not of this company" (type Error).</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
@@ -15436,7 +15436,7 @@
     <row r="47">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>M-045</t>
+          <t>M-075</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="E47" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Next number &lt;legacy next no&gt; is outside &lt;from no&gt;-&lt;to no&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The company has no Head Office branch for official receipts" (type Error).</t>
         </is>
       </c>
       <c r="F47" s="24" t="inlineStr">
@@ -15489,7 +15489,7 @@
     <row r="48">
       <c r="A48" s="22" t="inlineStr">
         <is>
-          <t>M-046</t>
+          <t>M-076</t>
         </is>
       </c>
       <c r="B48" s="22" t="inlineStr">
@@ -15509,7 +15509,7 @@
       </c>
       <c r="E48" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The last number cannot be below the numbers already issued" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Official receipt series belong to Head Office only" (type Error).</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
@@ -15542,7 +15542,7 @@
     <row r="49">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>M-047</t>
+          <t>M-077</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The last number must not be below the first number" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No authorized &lt;kind&gt; series with numbers left for this branch" (type Error).</t>
         </is>
       </c>
       <c r="F49" s="24" t="inlineStr">
@@ -15595,12 +15595,12 @@
     <row r="50">
       <c r="A50" s="22" t="inlineStr">
         <is>
-          <t>M-048</t>
+          <t>M-078</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
+          <t>Receipts, Issue Official Receipt and the receipt series (SCR</t>
         </is>
       </c>
       <c r="C50" s="22" t="inlineStr">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="E50" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No cancellation or reinstatement" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt series &lt;prefix&gt; is depleted" (type Error).</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
@@ -15648,12 +15648,12 @@
     <row r="51">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>M-049</t>
+          <t>M-079</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
+          <t>Receipts, Issue Official Receipt and the receipt series (SCR</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
@@ -15668,7 +15668,7 @@
       </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No items to display" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Next number &lt;legacy next no&gt; is outside &lt;from no&gt;-&lt;to no&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F51" s="24" t="inlineStr">
@@ -15701,12 +15701,12 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>M-050</t>
+          <t>M-080</t>
         </is>
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
+          <t>Receipts, Issue Official Receipt and the receipt series (SCR</t>
         </is>
       </c>
       <c r="C52" s="22" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="E52" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No journal posted yet" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The last number cannot be below the numbers already issued" (type Error).</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
@@ -15754,12 +15754,12 @@
     <row r="53">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>M-051</t>
+          <t>M-081</t>
         </is>
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
+          <t>Receipts, Issue Official Receipt and the receipt series (SCR</t>
         </is>
       </c>
       <c r="C53" s="24" t="inlineStr">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="E53" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Nothing applied from this receipt" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The last number must not be below the first number" (type Error).</t>
         </is>
       </c>
       <c r="F53" s="24" t="inlineStr">
@@ -15807,12 +15807,12 @@
     <row r="54">
       <c r="A54" s="22" t="inlineStr">
         <is>
-          <t>M-052</t>
+          <t>M-082</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
+          <t>Receipts, Issue Official Receipt and the receipt series (SCR</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="E54" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The requested action is applied to the receipt." (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The number format must hold the sequence {SEQ}" (type Error).</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
@@ -15860,7 +15860,7 @@
     <row r="55">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>M-053</t>
+          <t>M-083</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="E55" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The requester cannot approve &lt;transaction no&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No cancellation or reinstatement" (type Information).</t>
         </is>
       </c>
       <c r="F55" s="24" t="inlineStr">
@@ -15913,7 +15913,7 @@
     <row r="56">
       <c r="A56" s="22" t="inlineStr">
         <is>
-          <t>M-054</t>
+          <t>M-084</t>
         </is>
       </c>
       <c r="B56" s="22" t="inlineStr">
@@ -15933,7 +15933,7 @@
       </c>
       <c r="E56" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;transaction no&gt; is &lt;stage&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No items to display" (type Information).</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
@@ -15966,7 +15966,7 @@
     <row r="57">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>M-055</t>
+          <t>M-085</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="E57" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt &lt;receipt no&gt; already has a request waiting for approval" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No journal posted yet" (type Information).</t>
         </is>
       </c>
       <c r="F57" s="24" t="inlineStr">
@@ -16019,7 +16019,7 @@
     <row r="58">
       <c r="A58" s="22" t="inlineStr">
         <is>
-          <t>M-056</t>
+          <t>M-086</t>
         </is>
       </c>
       <c r="B58" s="22" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="E58" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt &lt;receipt no&gt; is already cancelled" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Nothing applied from this receipt" (type Information).</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
@@ -16072,7 +16072,7 @@
     <row r="59">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>M-057</t>
+          <t>M-087</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
@@ -16092,7 +16092,7 @@
       </c>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Unapplied item &lt;reference&gt; of the receipt is &lt;stage&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The requested action is applied to the receipt." (type Validation).</t>
         </is>
       </c>
       <c r="F59" s="24" t="inlineStr">
@@ -16125,7 +16125,7 @@
     <row r="60">
       <c r="A60" s="22" t="inlineStr">
         <is>
-          <t>M-058</t>
+          <t>M-088</t>
         </is>
       </c>
       <c r="B60" s="22" t="inlineStr">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="E60" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Only a cancelled receipt can be reinstated" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The requester cannot approve &lt;transaction no&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
@@ -16178,7 +16178,7 @@
     <row r="61">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>M-059</t>
+          <t>M-089</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
@@ -16198,7 +16198,7 @@
       </c>
       <c r="E61" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Select a reason" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;transaction no&gt; is &lt;stage&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F61" s="24" t="inlineStr">
@@ -16231,7 +16231,7 @@
     <row r="62">
       <c r="A62" s="22" t="inlineStr">
         <is>
-          <t>M-060</t>
+          <t>M-090</t>
         </is>
       </c>
       <c r="B62" s="22" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="E62" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Specify the reason when 'Others' is selected" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt &lt;receipt no&gt; already has a request waiting for approval" (type Error).</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
@@ -16284,7 +16284,7 @@
     <row r="63">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>M-061</t>
+          <t>M-091</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="E63" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The reinstated amount must be above zero and at most &lt;amount&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt &lt;receipt no&gt; is already cancelled" (type Error).</t>
         </is>
       </c>
       <c r="F63" s="24" t="inlineStr">
@@ -16337,7 +16337,7 @@
     <row r="64">
       <c r="A64" s="22" t="inlineStr">
         <is>
-          <t>M-062</t>
+          <t>M-092</t>
         </is>
       </c>
       <c r="B64" s="22" t="inlineStr">
@@ -16357,7 +16357,7 @@
       </c>
       <c r="E64" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the &lt;missing&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Unapplied item &lt;reference&gt; of the receipt is &lt;stage&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
@@ -16390,7 +16390,7 @@
     <row r="65">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>M-063</t>
+          <t>M-093</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="E65" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Premium reinstatement reasons apply to ARs" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Only a cancelled receipt can be reinstated" (type Error).</t>
         </is>
       </c>
       <c r="F65" s="24" t="inlineStr">
@@ -16443,12 +16443,12 @@
     <row r="66">
       <c r="A66" s="22" t="inlineStr">
         <is>
-          <t>M-064</t>
+          <t>M-094</t>
         </is>
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
+          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
@@ -16463,7 +16463,7 @@
       </c>
       <c r="E66" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Disposition updated" (type Confirmation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Select a reason" (type Error).</t>
         </is>
       </c>
       <c r="F66" s="22" t="inlineStr">
@@ -16496,12 +16496,12 @@
     <row r="67">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>M-065</t>
+          <t>M-095</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
+          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
@@ -16516,7 +16516,7 @@
       </c>
       <c r="E67" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No disposition yet" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Specify the reason when 'Others' is selected" (type Error).</t>
         </is>
       </c>
       <c r="F67" s="24" t="inlineStr">
@@ -16549,12 +16549,12 @@
     <row r="68">
       <c r="A68" s="22" t="inlineStr">
         <is>
-          <t>M-066</t>
+          <t>M-096</t>
         </is>
       </c>
       <c r="B68" s="22" t="inlineStr">
         <is>
-          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
+          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
         </is>
       </c>
       <c r="C68" s="22" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="E68" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The amount must be above zero and at most the balance &lt;balance&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The reinstated amount must be above zero and at most &lt;amount&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
@@ -16602,12 +16602,12 @@
     <row r="69">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>M-067</t>
+          <t>M-097</t>
         </is>
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
+          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="E69" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Invoice &lt;invoice no&gt; takes no client payment" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the &lt;missing&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F69" s="24" t="inlineStr">
@@ -16655,12 +16655,12 @@
     <row r="70">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>M-068</t>
+          <t>M-098</t>
         </is>
       </c>
       <c r="B70" s="22" t="inlineStr">
         <is>
-          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
+          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
         </is>
       </c>
       <c r="C70" s="22" t="inlineStr">
@@ -16675,7 +16675,7 @@
       </c>
       <c r="E70" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown invoice &lt;invoice no&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Premium reinstatement reasons apply to ARs" (type Error).</t>
         </is>
       </c>
       <c r="F70" s="22" t="inlineStr">
@@ -16708,12 +16708,12 @@
     <row r="71">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>M-069</t>
+          <t>M-099</t>
         </is>
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
+          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
         </is>
       </c>
       <c r="C71" s="24" t="inlineStr">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="E71" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;description&gt; needs the team leader's approval and is not processed at once" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Reinstatement of a cancelled receipt is not enabled (setting What Reinstate does)" (type Error).</t>
         </is>
       </c>
       <c r="F71" s="24" t="inlineStr">
@@ -16761,7 +16761,7 @@
     <row r="72">
       <c r="A72" s="22" t="inlineStr">
         <is>
-          <t>M-070</t>
+          <t>M-100</t>
         </is>
       </c>
       <c r="B72" s="22" t="inlineStr">
@@ -16781,7 +16781,7 @@
       </c>
       <c r="E72" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Invoice &lt;target invoice no&gt; has nothing outstanding to apply to" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Disposition updated" (type Confirmation).</t>
         </is>
       </c>
       <c r="F72" s="22" t="inlineStr">
@@ -16814,7 +16814,7 @@
     <row r="73">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>M-071</t>
+          <t>M-101</t>
         </is>
       </c>
       <c r="B73" s="24" t="inlineStr">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="E73" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No application" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No disposition yet" (type Information).</t>
         </is>
       </c>
       <c r="F73" s="24" t="inlineStr">
@@ -16867,7 +16867,7 @@
     <row r="74">
       <c r="A74" s="22" t="inlineStr">
         <is>
-          <t>M-072</t>
+          <t>M-102</t>
         </is>
       </c>
       <c r="B74" s="22" t="inlineStr">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="E74" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter &lt;what&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No unapplied payment matches the filters." (type Information).</t>
         </is>
       </c>
       <c r="F74" s="22" t="inlineStr">
@@ -16920,7 +16920,7 @@
     <row r="75">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>M-073</t>
+          <t>M-103</t>
         </is>
       </c>
       <c r="B75" s="24" t="inlineStr">
@@ -16940,7 +16940,7 @@
       </c>
       <c r="E75" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Disposition type &lt;type code&gt; has no processing rule" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The amount must be above zero and at most the balance &lt;balance&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F75" s="24" t="inlineStr">
@@ -16973,7 +16973,7 @@
     <row r="76">
       <c r="A76" s="22" t="inlineStr">
         <is>
-          <t>M-074</t>
+          <t>M-104</t>
         </is>
       </c>
       <c r="B76" s="22" t="inlineStr">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="E76" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A reclass or transfer moves the whole balance &lt;balance&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Invoice &lt;invoice no&gt; takes no client payment" (type Error).</t>
         </is>
       </c>
       <c r="F76" s="22" t="inlineStr">
@@ -17026,7 +17026,7 @@
     <row r="77">
       <c r="A77" s="24" t="inlineStr">
         <is>
-          <t>M-075</t>
+          <t>M-105</t>
         </is>
       </c>
       <c r="B77" s="24" t="inlineStr">
@@ -17046,7 +17046,7 @@
       </c>
       <c r="E77" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The requester cannot approve the disposition" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown invoice &lt;invoice no&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F77" s="24" t="inlineStr">
@@ -17079,7 +17079,7 @@
     <row r="78">
       <c r="A78" s="22" t="inlineStr">
         <is>
-          <t>M-076</t>
+          <t>M-106</t>
         </is>
       </c>
       <c r="B78" s="22" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="E78" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A refund is reversed only after Disbursement returned the request" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;description&gt; needs the team leader's approval and is not processed at once" (type Error).</t>
         </is>
       </c>
       <c r="F78" s="22" t="inlineStr">
@@ -17132,7 +17132,7 @@
     <row r="79">
       <c r="A79" s="24" t="inlineStr">
         <is>
-          <t>M-077</t>
+          <t>M-107</t>
         </is>
       </c>
       <c r="B79" s="24" t="inlineStr">
@@ -17152,7 +17152,7 @@
       </c>
       <c r="E79" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the reason for the reversal" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Invoice &lt;target invoice no&gt; has nothing outstanding to apply to" (type Error).</t>
         </is>
       </c>
       <c r="F79" s="24" t="inlineStr">
@@ -17185,7 +17185,7 @@
     <row r="80">
       <c r="A80" s="22" t="inlineStr">
         <is>
-          <t>M-078</t>
+          <t>M-108</t>
         </is>
       </c>
       <c r="B80" s="22" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="E80" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "An unapplied item needs an amount above zero" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No application" (type Error).</t>
         </is>
       </c>
       <c r="F80" s="22" t="inlineStr">
@@ -17238,7 +17238,7 @@
     <row r="81">
       <c r="A81" s="24" t="inlineStr">
         <is>
-          <t>M-079</t>
+          <t>M-109</t>
         </is>
       </c>
       <c r="B81" s="24" t="inlineStr">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="E81" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Amount &lt;value&gt; is above the unapplied balance &lt;balance&gt; of &lt;reference&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter &lt;what&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F81" s="24" t="inlineStr">
@@ -17291,7 +17291,7 @@
     <row r="82">
       <c r="A82" s="22" t="inlineStr">
         <is>
-          <t>M-080</t>
+          <t>M-110</t>
         </is>
       </c>
       <c r="B82" s="22" t="inlineStr">
@@ -17311,7 +17311,7 @@
       </c>
       <c r="E82" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;reference&gt; is &lt;stage&gt;, not &lt;stage&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Disposition type &lt;type code&gt; has no processing rule" (type Error).</t>
         </is>
       </c>
       <c r="F82" s="22" t="inlineStr">
@@ -17344,12 +17344,12 @@
     <row r="83">
       <c r="A83" s="24" t="inlineStr">
         <is>
-          <t>M-081</t>
+          <t>M-111</t>
         </is>
       </c>
       <c r="B83" s="24" t="inlineStr">
         <is>
-          <t>Incoming Requests (SCR-OP-13)</t>
+          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
         </is>
       </c>
       <c r="C83" s="24" t="inlineStr">
@@ -17364,7 +17364,7 @@
       </c>
       <c r="E83" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero and at most the unapplied balance" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A reclass or transfer moves the whole balance &lt;balance&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F83" s="24" t="inlineStr">
@@ -17397,12 +17397,12 @@
     <row r="84">
       <c r="A84" s="22" t="inlineStr">
         <is>
-          <t>M-082</t>
+          <t>M-112</t>
         </is>
       </c>
       <c r="B84" s="22" t="inlineStr">
         <is>
-          <t>Incoming Requests (SCR-OP-13)</t>
+          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
         </is>
       </c>
       <c r="C84" s="22" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="E84" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the client to reclass to" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The requester cannot approve the disposition" (type Error).</t>
         </is>
       </c>
       <c r="F84" s="22" t="inlineStr">
@@ -17450,12 +17450,12 @@
     <row r="85">
       <c r="A85" s="24" t="inlineStr">
         <is>
-          <t>M-083</t>
+          <t>M-113</t>
         </is>
       </c>
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>Incoming Requests (SCR-OP-13)</t>
+          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
         </is>
       </c>
       <c r="C85" s="24" t="inlineStr">
@@ -17470,7 +17470,7 @@
       </c>
       <c r="E85" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the marketing unit to transfer to" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A refund is reversed only after Disbursement returned the request" (type Error).</t>
         </is>
       </c>
       <c r="F85" s="24" t="inlineStr">
@@ -17503,12 +17503,12 @@
     <row r="86">
       <c r="A86" s="22" t="inlineStr">
         <is>
-          <t>M-084</t>
+          <t>M-114</t>
         </is>
       </c>
       <c r="B86" s="22" t="inlineStr">
         <is>
-          <t>Incoming Requests (SCR-OP-13)</t>
+          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
         </is>
       </c>
       <c r="C86" s="22" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="E86" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No collector requests to display" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the reason for the reversal" (type Error).</t>
         </is>
       </c>
       <c r="F86" s="22" t="inlineStr">
@@ -17556,12 +17556,12 @@
     <row r="87">
       <c r="A87" s="24" t="inlineStr">
         <is>
-          <t>M-085</t>
+          <t>M-115</t>
         </is>
       </c>
       <c r="B87" s="24" t="inlineStr">
         <is>
-          <t>Incoming Requests (SCR-OP-13)</t>
+          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
         </is>
       </c>
       <c r="C87" s="24" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="E87" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No payment reversals to display" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "An unapplied item needs an amount above zero" (type Error).</t>
         </is>
       </c>
       <c r="F87" s="24" t="inlineStr">
@@ -17609,12 +17609,12 @@
     <row r="88">
       <c r="A88" s="22" t="inlineStr">
         <is>
-          <t>M-086</t>
+          <t>M-116</t>
         </is>
       </c>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>Incoming Requests (SCR-OP-13)</t>
+          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
         </is>
       </c>
       <c r="C88" s="22" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="E88" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No refund validations to display" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Amount &lt;value&gt; is above the unapplied balance &lt;balance&gt; of &lt;reference&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F88" s="22" t="inlineStr">
@@ -17662,12 +17662,12 @@
     <row r="89">
       <c r="A89" s="24" t="inlineStr">
         <is>
-          <t>M-087</t>
+          <t>M-117</t>
         </is>
       </c>
       <c r="B89" s="24" t="inlineStr">
         <is>
-          <t>Incoming Requests (SCR-OP-13)</t>
+          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
         </is>
       </c>
       <c r="C89" s="24" t="inlineStr">
@@ -17682,7 +17682,7 @@
       </c>
       <c r="E89" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The selected receipt is reversed as requested." (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;reference&gt; is &lt;stage&gt;, not &lt;stage&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F89" s="24" t="inlineStr">
@@ -17715,7 +17715,7 @@
     <row r="90">
       <c r="A90" s="22" t="inlineStr">
         <is>
-          <t>M-088</t>
+          <t>M-118</t>
         </is>
       </c>
       <c r="B90" s="22" t="inlineStr">
@@ -17735,7 +17735,7 @@
       </c>
       <c r="E90" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;request no&gt; is already &lt;status&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero and at most the unapplied balance" (type Validation).</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
@@ -17768,7 +17768,7 @@
     <row r="91">
       <c r="A91" s="24" t="inlineStr">
         <is>
-          <t>M-089</t>
+          <t>M-119</t>
         </is>
       </c>
       <c r="B91" s="24" t="inlineStr">
@@ -17788,7 +17788,7 @@
       </c>
       <c r="E91" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Disposition type &lt;type&gt; does not carry out a &lt;action&gt; request" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the client to reclass to" (type Validation).</t>
         </is>
       </c>
       <c r="F91" s="24" t="inlineStr">
@@ -17821,7 +17821,7 @@
     <row r="92">
       <c r="A92" s="22" t="inlineStr">
         <is>
-          <t>M-090</t>
+          <t>M-120</t>
         </is>
       </c>
       <c r="B92" s="22" t="inlineStr">
@@ -17841,7 +17841,7 @@
       </c>
       <c r="E92" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown disposition type &lt;type&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the marketing unit to transfer to" (type Validation).</t>
         </is>
       </c>
       <c r="F92" s="22" t="inlineStr">
@@ -17874,7 +17874,7 @@
     <row r="93">
       <c r="A93" s="24" t="inlineStr">
         <is>
-          <t>M-091</t>
+          <t>M-121</t>
         </is>
       </c>
       <c r="B93" s="24" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="E93" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The requester cannot approve the payment reversal" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No collector requests to display" (type Information).</t>
         </is>
       </c>
       <c r="F93" s="24" t="inlineStr">
@@ -17927,7 +17927,7 @@
     <row r="94">
       <c r="A94" s="22" t="inlineStr">
         <is>
-          <t>M-092</t>
+          <t>M-122</t>
         </is>
       </c>
       <c r="B94" s="22" t="inlineStr">
@@ -17947,7 +17947,7 @@
       </c>
       <c r="E94" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;request no&gt; is already &lt;status&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No payment reversals to display" (type Information).</t>
         </is>
       </c>
       <c r="F94" s="22" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="95">
       <c r="A95" s="24" t="inlineStr">
         <is>
-          <t>M-093</t>
+          <t>M-123</t>
         </is>
       </c>
       <c r="B95" s="24" t="inlineStr">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="E95" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt &lt;receipt no&gt; has &lt;available&gt; applied to &lt;invoice no&gt;, less than &lt;target&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No refund validations to display" (type Information).</t>
         </is>
       </c>
       <c r="F95" s="24" t="inlineStr">
@@ -18033,7 +18033,7 @@
     <row r="96">
       <c r="A96" s="22" t="inlineStr">
         <is>
-          <t>M-094</t>
+          <t>M-124</t>
         </is>
       </c>
       <c r="B96" s="22" t="inlineStr">
@@ -18053,7 +18053,7 @@
       </c>
       <c r="E96" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown receipt &lt;receipt no&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The selected receipt is reversed as requested." (type Validation).</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
@@ -18086,7 +18086,7 @@
     <row r="97">
       <c r="A97" s="24" t="inlineStr">
         <is>
-          <t>M-095</t>
+          <t>M-125</t>
         </is>
       </c>
       <c r="B97" s="24" t="inlineStr">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="E97" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;task no&gt; is already &lt;status&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;request no&gt; is already &lt;status&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F97" s="24" t="inlineStr">
@@ -18139,7 +18139,7 @@
     <row r="98">
       <c r="A98" s="22" t="inlineStr">
         <is>
-          <t>M-096</t>
+          <t>M-126</t>
         </is>
       </c>
       <c r="B98" s="22" t="inlineStr">
@@ -18159,7 +18159,7 @@
       </c>
       <c r="E98" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Choose the unapplied item that holds the returned premium" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Disposition type &lt;type&gt; does not carry out a &lt;action&gt; request" (type Error).</t>
         </is>
       </c>
       <c r="F98" s="22" t="inlineStr">
@@ -18192,7 +18192,7 @@
     <row r="99">
       <c r="A99" s="24" t="inlineStr">
         <is>
-          <t>M-097</t>
+          <t>M-127</t>
         </is>
       </c>
       <c r="B99" s="24" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="E99" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the reason for rejecting" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown disposition type &lt;type&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F99" s="24" t="inlineStr">
@@ -18245,12 +18245,12 @@
     <row r="100">
       <c r="A100" s="22" t="inlineStr">
         <is>
-          <t>M-098</t>
+          <t>M-128</t>
         </is>
       </c>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>Pre-booked Payments (SCR-OP-14)</t>
+          <t>Incoming Requests (SCR-OP-13)</t>
         </is>
       </c>
       <c r="C100" s="22" t="inlineStr">
@@ -18265,7 +18265,7 @@
       </c>
       <c r="E100" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No items to display" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The requester cannot approve the payment reversal" (type Error).</t>
         </is>
       </c>
       <c r="F100" s="22" t="inlineStr">
@@ -18298,12 +18298,12 @@
     <row r="101">
       <c r="A101" s="24" t="inlineStr">
         <is>
-          <t>M-099</t>
+          <t>M-129</t>
         </is>
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>Pre-booked Payments (SCR-OP-14)</t>
+          <t>Incoming Requests (SCR-OP-13)</t>
         </is>
       </c>
       <c r="C101" s="24" t="inlineStr">
@@ -18318,7 +18318,7 @@
       </c>
       <c r="E101" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Pre-booked payment of &lt;arn&gt; is &lt;status&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;request no&gt; is already &lt;status&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F101" s="24" t="inlineStr">
@@ -18351,12 +18351,12 @@
     <row r="102">
       <c r="A102" s="22" t="inlineStr">
         <is>
-          <t>M-100</t>
+          <t>M-130</t>
         </is>
       </c>
       <c r="B102" s="22" t="inlineStr">
         <is>
-          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
+          <t>Incoming Requests (SCR-OP-13)</t>
         </is>
       </c>
       <c r="C102" s="22" t="inlineStr">
@@ -18371,7 +18371,7 @@
       </c>
       <c r="E102" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Layout of &lt;handler code&gt; saved" (type Confirmation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt &lt;receipt no&gt; has &lt;available&gt; applied to &lt;invoice no&gt;, less than &lt;target&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F102" s="22" t="inlineStr">
@@ -18404,12 +18404,12 @@
     <row r="103">
       <c r="A103" s="24" t="inlineStr">
         <is>
-          <t>M-101</t>
+          <t>M-131</t>
         </is>
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
+          <t>Incoming Requests (SCR-OP-13)</t>
         </is>
       </c>
       <c r="C103" s="24" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="E103" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No payment accepted in this run" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown receipt &lt;receipt no&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F103" s="24" t="inlineStr">
@@ -18457,12 +18457,12 @@
     <row r="104">
       <c r="A104" s="22" t="inlineStr">
         <is>
-          <t>M-102</t>
+          <t>M-132</t>
         </is>
       </c>
       <c r="B104" s="22" t="inlineStr">
         <is>
-          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
+          <t>Incoming Requests (SCR-OP-13)</t>
         </is>
       </c>
       <c r="C104" s="22" t="inlineStr">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="E104" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Sweep done: &lt;premium&gt; premium balance(s) reversed, &lt;excess&gt; excess moved to overages" (type Confirmation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;task no&gt; is already &lt;status&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F104" s="22" t="inlineStr">
@@ -18510,12 +18510,12 @@
     <row r="105">
       <c r="A105" s="24" t="inlineStr">
         <is>
-          <t>M-103</t>
+          <t>M-133</t>
         </is>
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
+          <t>Incoming Requests (SCR-OP-13)</t>
         </is>
       </c>
       <c r="C105" s="24" t="inlineStr">
@@ -18530,7 +18530,7 @@
       </c>
       <c r="E105" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A delimited layout needs a one-character separator" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Choose the unapplied item that holds the returned premium" (type Error).</t>
         </is>
       </c>
       <c r="F105" s="24" t="inlineStr">
@@ -18563,12 +18563,12 @@
     <row r="106">
       <c r="A106" s="22" t="inlineStr">
         <is>
-          <t>M-104</t>
+          <t>M-134</t>
         </is>
       </c>
       <c r="B106" s="22" t="inlineStr">
         <is>
-          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
+          <t>Incoming Requests (SCR-OP-13)</t>
         </is>
       </c>
       <c r="C106" s="22" t="inlineStr">
@@ -18583,7 +18583,7 @@
       </c>
       <c r="E106" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A fixed-width layout needs its fields" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the reason for rejecting" (type Error).</t>
         </is>
       </c>
       <c r="F106" s="22" t="inlineStr">
@@ -18616,12 +18616,12 @@
     <row r="107">
       <c r="A107" s="24" t="inlineStr">
         <is>
-          <t>M-105</t>
+          <t>M-135</t>
         </is>
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
+          <t>Pre-booked Payments (SCR-OP-14)</t>
         </is>
       </c>
       <c r="C107" s="24" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="E107" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Start and length of '&lt;part&gt;' must be numbers" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No items to display" (type Information).</t>
         </is>
       </c>
       <c r="F107" s="24" t="inlineStr">
@@ -18669,12 +18669,12 @@
     <row r="108">
       <c r="A108" s="22" t="inlineStr">
         <is>
-          <t>M-106</t>
+          <t>M-136</t>
         </is>
       </c>
       <c r="B108" s="22" t="inlineStr">
         <is>
-          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
+          <t>Pre-booked Payments (SCR-OP-14)</t>
         </is>
       </c>
       <c r="C108" s="22" t="inlineStr">
@@ -18689,7 +18689,7 @@
       </c>
       <c r="E108" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Write each field as Header:start:length, not '&lt;part&gt;'" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Pre-booked payment of &lt;arn&gt; is &lt;status&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
@@ -18722,7 +18722,7 @@
     <row r="109">
       <c r="A109" s="24" t="inlineStr">
         <is>
-          <t>M-107</t>
+          <t>M-137</t>
         </is>
       </c>
       <c r="B109" s="24" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="E109" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown layout kind &lt;new kind&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Layout of &lt;handler code&gt; saved" (type Confirmation).</t>
         </is>
       </c>
       <c r="F109" s="24" t="inlineStr">
@@ -18775,12 +18775,12 @@
     <row r="110">
       <c r="A110" s="22" t="inlineStr">
         <is>
-          <t>M-108</t>
+          <t>M-138</t>
         </is>
       </c>
       <c r="B110" s="22" t="inlineStr">
         <is>
-          <t>PDC Warehouse (SCR-OP-16)</t>
+          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
         </is>
       </c>
       <c r="C110" s="22" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="E110" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No payment accepted in this run" (type Information).</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
@@ -18828,12 +18828,12 @@
     <row r="111">
       <c r="A111" s="24" t="inlineStr">
         <is>
-          <t>M-109</t>
+          <t>M-139</t>
         </is>
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>PDC Warehouse (SCR-OP-16)</t>
+          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
         </is>
       </c>
       <c r="C111" s="24" t="inlineStr">
@@ -18848,7 +18848,7 @@
       </c>
       <c r="E111" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "PDC warehouse updated" (type Confirmation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Sweep done: &lt;premium&gt; reversed, &lt;excess&gt; excess moved to overages" (type Confirmation).</t>
         </is>
       </c>
       <c r="F111" s="24" t="inlineStr">
@@ -18881,12 +18881,12 @@
     <row r="112">
       <c r="A112" s="22" t="inlineStr">
         <is>
-          <t>M-110</t>
+          <t>M-140</t>
         </is>
       </c>
       <c r="B112" s="22" t="inlineStr">
         <is>
-          <t>PDC Warehouse (SCR-OP-16)</t>
+          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
         </is>
       </c>
       <c r="C112" s="22" t="inlineStr">
@@ -18901,7 +18901,7 @@
       </c>
       <c r="E112" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A post-dated check needs an amount above zero" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A delimited layout needs a one-character separator" (type Error).</t>
         </is>
       </c>
       <c r="F112" s="22" t="inlineStr">
@@ -18934,12 +18934,12 @@
     <row r="113">
       <c r="A113" s="24" t="inlineStr">
         <is>
-          <t>M-111</t>
+          <t>M-141</t>
         </is>
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>PDC Warehouse (SCR-OP-16)</t>
+          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
         </is>
       </c>
       <c r="C113" s="24" t="inlineStr">
@@ -18954,7 +18954,7 @@
       </c>
       <c r="E113" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Check &lt;bank code&gt; &lt;check no&gt; is already warehoused" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A fixed-width layout needs its fields" (type Error).</t>
         </is>
       </c>
       <c r="F113" s="24" t="inlineStr">
@@ -18987,12 +18987,12 @@
     <row r="114">
       <c r="A114" s="22" t="inlineStr">
         <is>
-          <t>M-112</t>
+          <t>M-142</t>
         </is>
       </c>
       <c r="B114" s="22" t="inlineStr">
         <is>
-          <t>PDC Warehouse (SCR-OP-16)</t>
+          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
         </is>
       </c>
       <c r="C114" s="22" t="inlineStr">
@@ -19007,7 +19007,7 @@
       </c>
       <c r="E114" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Check &lt;warehouse no&gt; is &lt;status&gt;, not in the warehouse" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Start and length of '&lt;part&gt;' must be numbers" (type Error).</t>
         </is>
       </c>
       <c r="F114" s="22" t="inlineStr">
@@ -19040,12 +19040,12 @@
     <row r="115">
       <c r="A115" s="24" t="inlineStr">
         <is>
-          <t>M-113</t>
+          <t>M-143</t>
         </is>
       </c>
       <c r="B115" s="24" t="inlineStr">
         <is>
-          <t>PDC Warehouse (SCR-OP-16)</t>
+          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
         </is>
       </c>
       <c r="C115" s="24" t="inlineStr">
@@ -19060,7 +19060,7 @@
       </c>
       <c r="E115" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A check leaves the warehouse as returned, replaced or pulled out" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Write each field as Header:start:length, not '&lt;part&gt;'" (type Error).</t>
         </is>
       </c>
       <c r="F115" s="24" t="inlineStr">
@@ -19093,12 +19093,12 @@
     <row r="116">
       <c r="A116" s="22" t="inlineStr">
         <is>
-          <t>M-114</t>
+          <t>M-144</t>
         </is>
       </c>
       <c r="B116" s="22" t="inlineStr">
         <is>
-          <t>Batch Print (SCR-OP-18)</t>
+          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
         </is>
       </c>
       <c r="C116" s="22" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="E116" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;batch no&gt;: &lt;printed count&gt; printed, &lt;failed count&gt; failed" (type Confirmation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown layout kind &lt;new kind&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F116" s="22" t="inlineStr">
@@ -19146,12 +19146,12 @@
     <row r="117">
       <c r="A117" s="24" t="inlineStr">
         <is>
-          <t>M-115</t>
+          <t>M-145</t>
         </is>
       </c>
       <c r="B117" s="24" t="inlineStr">
         <is>
-          <t>Batch Print (SCR-OP-18)</t>
+          <t>PDC Warehouse (SCR-OP-16)</t>
         </is>
       </c>
       <c r="C117" s="24" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="E117" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No print batch yet" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero" (type Validation).</t>
         </is>
       </c>
       <c r="F117" s="24" t="inlineStr">
@@ -19199,12 +19199,12 @@
     <row r="118">
       <c r="A118" s="22" t="inlineStr">
         <is>
-          <t>M-116</t>
+          <t>M-146</t>
         </is>
       </c>
       <c r="B118" s="22" t="inlineStr">
         <is>
-          <t>Batch Print (SCR-OP-18)</t>
+          <t>PDC Warehouse (SCR-OP-16)</t>
         </is>
       </c>
       <c r="C118" s="22" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="E118" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No receipts match the criteria" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No post-dated checks" (type Information).</t>
         </is>
       </c>
       <c r="F118" s="22" t="inlineStr">
@@ -19252,12 +19252,12 @@
     <row r="119">
       <c r="A119" s="24" t="inlineStr">
         <is>
-          <t>M-117</t>
+          <t>M-147</t>
         </is>
       </c>
       <c r="B119" s="24" t="inlineStr">
         <is>
-          <t>Batch Print (SCR-OP-18)</t>
+          <t>PDC Warehouse (SCR-OP-16)</t>
         </is>
       </c>
       <c r="C119" s="24" t="inlineStr">
@@ -19272,7 +19272,7 @@
       </c>
       <c r="E119" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt &lt;receipt no&gt; is cancelled" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "PDC warehouse updated" (type Confirmation).</t>
         </is>
       </c>
       <c r="F119" s="24" t="inlineStr">
@@ -19305,12 +19305,12 @@
     <row r="120">
       <c r="A120" s="22" t="inlineStr">
         <is>
-          <t>M-118</t>
+          <t>M-148</t>
         </is>
       </c>
       <c r="B120" s="22" t="inlineStr">
         <is>
-          <t>Batch Print (SCR-OP-18)</t>
+          <t>PDC Warehouse (SCR-OP-16)</t>
         </is>
       </c>
       <c r="C120" s="22" t="inlineStr">
@@ -19325,7 +19325,7 @@
       </c>
       <c r="E120" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;batch no&gt; has no failures" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A post-dated check needs an amount above zero" (type Error).</t>
         </is>
       </c>
       <c r="F120" s="22" t="inlineStr">
@@ -19358,12 +19358,12 @@
     <row r="121">
       <c r="A121" s="24" t="inlineStr">
         <is>
-          <t>M-119</t>
+          <t>M-149</t>
         </is>
       </c>
       <c r="B121" s="24" t="inlineStr">
         <is>
-          <t>Batch Print (SCR-OP-18)</t>
+          <t>PDC Warehouse (SCR-OP-16)</t>
         </is>
       </c>
       <c r="C121" s="24" t="inlineStr">
@@ -19378,7 +19378,7 @@
       </c>
       <c r="E121" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Select between 1 and 500 receipts to print" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Check &lt;bank code&gt; &lt;check no&gt; is already warehoused" (type Error).</t>
         </is>
       </c>
       <c r="F121" s="24" t="inlineStr">
@@ -19411,12 +19411,12 @@
     <row r="122">
       <c r="A122" s="22" t="inlineStr">
         <is>
-          <t>M-140</t>
+          <t>M-150</t>
         </is>
       </c>
       <c r="B122" s="22" t="inlineStr">
         <is>
-          <t>Commission ORs (SCR-OP-20)</t>
+          <t>PDC Warehouse (SCR-OP-16)</t>
         </is>
       </c>
       <c r="C122" s="22" t="inlineStr">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="E122" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No commission payment waiting for an OR" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Check &lt;warehouse no&gt; is &lt;status&gt;, not in the warehouse" (type Error).</t>
         </is>
       </c>
       <c r="F122" s="22" t="inlineStr">
@@ -19464,12 +19464,12 @@
     <row r="123">
       <c r="A123" s="24" t="inlineStr">
         <is>
-          <t>M-141</t>
+          <t>M-151</t>
         </is>
       </c>
       <c r="B123" s="24" t="inlineStr">
         <is>
-          <t>Commission ORs (SCR-OP-20)</t>
+          <t>PDC Warehouse (SCR-OP-16)</t>
         </is>
       </c>
       <c r="C123" s="24" t="inlineStr">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="E123" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown company &lt;company&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A check leaves the warehouse as returned, replaced or pulled out" (type Error).</t>
         </is>
       </c>
       <c r="F123" s="24" t="inlineStr">
@@ -19517,12 +19517,12 @@
     <row r="124">
       <c r="A124" s="22" t="inlineStr">
         <is>
-          <t>M-351</t>
+          <t>M-152</t>
         </is>
       </c>
       <c r="B124" s="22" t="inlineStr">
         <is>
-          <t>Interfaces (SCR-OP-61)</t>
+          <t>Batch Print (SCR-OP-18)</t>
         </is>
       </c>
       <c r="C124" s="22" t="inlineStr">
@@ -19537,7 +19537,7 @@
       </c>
       <c r="E124" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;name&gt; saved" (type Confirmation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;batch no&gt;: &lt;printed count&gt; printed, &lt;failed count&gt; not printed" (type Confirmation).</t>
         </is>
       </c>
       <c r="F124" s="22" t="inlineStr">
@@ -19570,12 +19570,12 @@
     <row r="125">
       <c r="A125" s="24" t="inlineStr">
         <is>
-          <t>M-352</t>
+          <t>M-153</t>
         </is>
       </c>
       <c r="B125" s="24" t="inlineStr">
         <is>
-          <t>Interfaces (SCR-OP-61)</t>
+          <t>Batch Print (SCR-OP-18)</t>
         </is>
       </c>
       <c r="C125" s="24" t="inlineStr">
@@ -19590,7 +19590,7 @@
       </c>
       <c r="E125" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No records in this run" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt &lt;receipt no&gt; is cancelled" (type Error).</t>
         </is>
       </c>
       <c r="F125" s="24" t="inlineStr">
@@ -19623,12 +19623,12 @@
     <row r="126">
       <c r="A126" s="22" t="inlineStr">
         <is>
-          <t>M-353</t>
+          <t>M-154</t>
         </is>
       </c>
       <c r="B126" s="22" t="inlineStr">
         <is>
-          <t>Interfaces (SCR-OP-61)</t>
+          <t>Batch Print (SCR-OP-18)</t>
         </is>
       </c>
       <c r="C126" s="22" t="inlineStr">
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E126" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No runs yet" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;batch no&gt; has no failure to skip" (type Error).</t>
         </is>
       </c>
       <c r="F126" s="22" t="inlineStr">
@@ -19676,12 +19676,12 @@
     <row r="127">
       <c r="A127" s="24" t="inlineStr">
         <is>
-          <t>M-354</t>
+          <t>M-155</t>
         </is>
       </c>
       <c r="B127" s="24" t="inlineStr">
         <is>
-          <t>Interfaces (SCR-OP-61)</t>
+          <t>Batch Print (SCR-OP-18)</t>
         </is>
       </c>
       <c r="C127" s="24" t="inlineStr">
@@ -19696,7 +19696,7 @@
       </c>
       <c r="E127" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Feed &lt;code&gt; is inactive" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;batch no&gt; has no failures" (type Error).</t>
         </is>
       </c>
       <c r="F127" s="24" t="inlineStr">
@@ -19729,12 +19729,12 @@
     <row r="128">
       <c r="A128" s="22" t="inlineStr">
         <is>
-          <t>M-355</t>
+          <t>M-156</t>
         </is>
       </c>
       <c r="B128" s="22" t="inlineStr">
         <is>
-          <t>Interfaces (SCR-OP-61)</t>
+          <t>Batch Print (SCR-OP-18)</t>
         </is>
       </c>
       <c r="C128" s="22" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E128" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No module processes uploads of feed &lt;feed code&gt; yet" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;batch no&gt; has no ZIP of its receipts" (type Error).</t>
         </is>
       </c>
       <c r="F128" s="22" t="inlineStr">
@@ -19782,12 +19782,12 @@
     <row r="129">
       <c r="A129" s="24" t="inlineStr">
         <is>
-          <t>M-356</t>
+          <t>M-157</t>
         </is>
       </c>
       <c r="B129" s="24" t="inlineStr">
         <is>
-          <t>Several screens</t>
+          <t>Batch Print (SCR-OP-18)</t>
         </is>
       </c>
       <c r="C129" s="24" t="inlineStr">
@@ -19802,7 +19802,7 @@
       </c>
       <c r="E129" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No receipt series yet" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Select between 1 and 500 receipts to print" (type Error).</t>
         </is>
       </c>
       <c r="F129" s="24" t="inlineStr">
@@ -19835,12 +19835,12 @@
     <row r="130">
       <c r="A130" s="22" t="inlineStr">
         <is>
-          <t>M-357</t>
+          <t>M-178</t>
         </is>
       </c>
       <c r="B130" s="22" t="inlineStr">
         <is>
-          <t>Several screens</t>
+          <t>Commission ORs (SCR-OP-20)</t>
         </is>
       </c>
       <c r="C130" s="22" t="inlineStr">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="E130" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Prefix is required" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No commission payment waiting for an OR" (type Information).</t>
         </is>
       </c>
       <c r="F130" s="22" t="inlineStr">
@@ -19888,12 +19888,12 @@
     <row r="131">
       <c r="A131" s="24" t="inlineStr">
         <is>
-          <t>M-358</t>
+          <t>M-179</t>
         </is>
       </c>
       <c r="B131" s="24" t="inlineStr">
         <is>
-          <t>Several screens</t>
+          <t>Commission ORs (SCR-OP-20)</t>
         </is>
       </c>
       <c r="C131" s="24" t="inlineStr">
@@ -19908,7 +19908,7 @@
       </c>
       <c r="E131" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Series &lt;prefix&gt; saved" (type Confirmation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown company &lt;company&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F131" s="24" t="inlineStr">
@@ -19941,12 +19941,12 @@
     <row r="132">
       <c r="A132" s="22" t="inlineStr">
         <is>
-          <t>M-359</t>
+          <t>M-389</t>
         </is>
       </c>
       <c r="B132" s="22" t="inlineStr">
         <is>
-          <t>Several screens</t>
+          <t>Interfaces (SCR-OP-61)</t>
         </is>
       </c>
       <c r="C132" s="22" t="inlineStr">
@@ -19961,7 +19961,7 @@
       </c>
       <c r="E132" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The range must end at or after its start" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;name&gt; saved" (type Confirmation).</t>
         </is>
       </c>
       <c r="F132" s="22" t="inlineStr">
@@ -19994,12 +19994,12 @@
     <row r="133">
       <c r="A133" s="24" t="inlineStr">
         <is>
-          <t>M-360</t>
+          <t>M-390</t>
         </is>
       </c>
       <c r="B133" s="24" t="inlineStr">
         <is>
-          <t>Several screens</t>
+          <t>Interfaces (SCR-OP-61)</t>
         </is>
       </c>
       <c r="C133" s="24" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="E133" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The series becomes active for issuing receipts." (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No records in this run" (type Information).</t>
         </is>
       </c>
       <c r="F133" s="24" t="inlineStr">
@@ -20047,12 +20047,12 @@
     <row r="134">
       <c r="A134" s="22" t="inlineStr">
         <is>
-          <t>M-361</t>
+          <t>M-391</t>
         </is>
       </c>
       <c r="B134" s="22" t="inlineStr">
         <is>
-          <t>Upload screens (Payment Uploads, BIR 2307, Commission ORs, B</t>
+          <t>Interfaces (SCR-OP-61)</t>
         </is>
       </c>
       <c r="C134" s="22" t="inlineStr">
@@ -20067,7 +20067,7 @@
       </c>
       <c r="E134" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No runs yet" (type Information).</t>
         </is>
       </c>
       <c r="F134" s="22" t="inlineStr">
@@ -20100,12 +20100,12 @@
     <row r="135">
       <c r="A135" s="24" t="inlineStr">
         <is>
-          <t>M-362</t>
+          <t>M-392</t>
         </is>
       </c>
       <c r="B135" s="24" t="inlineStr">
         <is>
-          <t>Upload screens (Payment Uploads, BIR 2307, Commission ORs, B</t>
+          <t>Interfaces (SCR-OP-61)</t>
         </is>
       </c>
       <c r="C135" s="24" t="inlineStr">
@@ -20120,7 +20120,7 @@
       </c>
       <c r="E135" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;Column&gt; is mandatory" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Feed &lt;code&gt; is inactive" (type Error).</t>
         </is>
       </c>
       <c r="F135" s="24" t="inlineStr">
@@ -20153,12 +20153,12 @@
     <row r="136">
       <c r="A136" s="22" t="inlineStr">
         <is>
-          <t>M-366</t>
+          <t>M-393</t>
         </is>
       </c>
       <c r="B136" s="22" t="inlineStr">
         <is>
-          <t>Upload screens (Payment Uploads, BIR 2307, Commission ORs, B</t>
+          <t>Interfaces (SCR-OP-61)</t>
         </is>
       </c>
       <c r="C136" s="22" t="inlineStr">
@@ -20173,7 +20173,7 @@
       </c>
       <c r="E136" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The amount must be above zero" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No module processes uploads of feed &lt;feed code&gt; yet" (type Error).</t>
         </is>
       </c>
       <c r="F136" s="22" t="inlineStr">
@@ -20206,12 +20206,12 @@
     <row r="137">
       <c r="A137" s="24" t="inlineStr">
         <is>
-          <t>M-367</t>
+          <t>M-394</t>
         </is>
       </c>
       <c r="B137" s="24" t="inlineStr">
         <is>
-          <t>Upload screens (Payment Uploads, BIR 2307, Commission ORs, B</t>
+          <t>Several screens</t>
         </is>
       </c>
       <c r="C137" s="24" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="E137" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The basic commission must be above zero" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No receipt series yet" (type Information).</t>
         </is>
       </c>
       <c r="F137" s="24" t="inlineStr">
@@ -20259,12 +20259,12 @@
     <row r="138">
       <c r="A138" s="22" t="inlineStr">
         <is>
-          <t>M-368</t>
+          <t>M-395</t>
         </is>
       </c>
       <c r="B138" s="22" t="inlineStr">
         <is>
-          <t>Every screen (Common screen elements)</t>
+          <t>Several screens</t>
         </is>
       </c>
       <c r="C138" s="22" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="E138" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "You are not permitted to perform this action" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Nothing to show" (type Information).</t>
         </is>
       </c>
       <c r="F138" s="22" t="inlineStr">
@@ -20312,12 +20312,12 @@
     <row r="139">
       <c r="A139" s="24" t="inlineStr">
         <is>
-          <t>M-369</t>
+          <t>M-396</t>
         </is>
       </c>
       <c r="B139" s="24" t="inlineStr">
         <is>
-          <t>Every screen (Common screen elements)</t>
+          <t>Several screens</t>
         </is>
       </c>
       <c r="C139" s="24" t="inlineStr">
@@ -20332,7 +20332,7 @@
       </c>
       <c r="E139" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The record was changed by another user. Please reload and try again." (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Prefix is required" (type Validation).</t>
         </is>
       </c>
       <c r="F139" s="24" t="inlineStr">
@@ -20365,12 +20365,12 @@
     <row r="140">
       <c r="A140" s="22" t="inlineStr">
         <is>
-          <t>M-370</t>
+          <t>M-397</t>
         </is>
       </c>
       <c r="B140" s="22" t="inlineStr">
         <is>
-          <t>Every screen (Common screen elements)</t>
+          <t>Several screens</t>
         </is>
       </c>
       <c r="C140" s="22" t="inlineStr">
@@ -20385,7 +20385,7 @@
       </c>
       <c r="E140" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The system could not complete the request. Try again; if it continues, contact support with the reference." (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Series &lt;prefix&gt; saved" (type Confirmation).</t>
         </is>
       </c>
       <c r="F140" s="22" t="inlineStr">
@@ -20418,12 +20418,12 @@
     <row r="141">
       <c r="A141" s="24" t="inlineStr">
         <is>
-          <t>M-371</t>
+          <t>M-398</t>
         </is>
       </c>
       <c r="B141" s="24" t="inlineStr">
         <is>
-          <t>Every screen (Common screen elements)</t>
+          <t>Several screens</t>
         </is>
       </c>
       <c r="C141" s="24" t="inlineStr">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="E141" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Parameter '&lt;name&gt;' has an invalid value" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The number format must hold the sequence {SEQ}" (type Validation).</t>
         </is>
       </c>
       <c r="F141" s="24" t="inlineStr">
@@ -20471,12 +20471,12 @@
     <row r="142">
       <c r="A142" s="22" t="inlineStr">
         <is>
-          <t>M-372</t>
+          <t>M-399</t>
         </is>
       </c>
       <c r="B142" s="22" t="inlineStr">
         <is>
-          <t>Every screen (Common screen elements)</t>
+          <t>Several screens</t>
         </is>
       </c>
       <c r="C142" s="22" t="inlineStr">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="E142" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Required parameter '&lt;parameter name&gt;' is missing" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The range must end at or after its start" (type Validation).</t>
         </is>
       </c>
       <c r="F142" s="22" t="inlineStr">
@@ -20524,12 +20524,12 @@
     <row r="143">
       <c r="A143" s="24" t="inlineStr">
         <is>
-          <t>M-373</t>
+          <t>M-400</t>
         </is>
       </c>
       <c r="B143" s="24" t="inlineStr">
         <is>
-          <t>Every screen (Common screen elements)</t>
+          <t>Several screens</t>
         </is>
       </c>
       <c r="C143" s="24" t="inlineStr">
@@ -20544,7 +20544,7 @@
       </c>
       <c r="E143" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The uploaded file is too large" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The series becomes active for issuing receipts." (type Validation).</t>
         </is>
       </c>
       <c r="F143" s="24" t="inlineStr">
@@ -20577,12 +20577,12 @@
     <row r="144">
       <c r="A144" s="22" t="inlineStr">
         <is>
-          <t>M-374</t>
+          <t>M-401</t>
         </is>
       </c>
       <c r="B144" s="22" t="inlineStr">
         <is>
-          <t>Every screen (Common screen elements)</t>
+          <t>Upload screens (Payment Uploads, BIR 2307, Commission ORs, B</t>
         </is>
       </c>
       <c r="C144" s="22" t="inlineStr">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="E144" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Invalid request" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;" (type Validation).</t>
         </is>
       </c>
       <c r="F144" s="22" t="inlineStr">
@@ -20627,8 +20627,962 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="24" t="inlineStr">
+        <is>
+          <t>M-402</t>
+        </is>
+      </c>
+      <c r="B145" s="24" t="inlineStr">
+        <is>
+          <t>Upload screens (Payment Uploads, BIR 2307, Commission ORs, B</t>
+        </is>
+      </c>
+      <c r="C145" s="24" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D145" s="24" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E145" s="24" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;Column&gt; is mandatory" (type Validation).</t>
+        </is>
+      </c>
+      <c r="F145" s="24" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G145" s="24" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H145" s="24" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I145" s="24" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J145" s="24" t="inlineStr"/>
+      <c r="K145" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="22" t="inlineStr">
+        <is>
+          <t>M-406</t>
+        </is>
+      </c>
+      <c r="B146" s="22" t="inlineStr">
+        <is>
+          <t>Upload screens (Payment Uploads, BIR 2307, Commission ORs, B</t>
+        </is>
+      </c>
+      <c r="C146" s="22" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D146" s="22" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E146" s="22" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The amount must be above zero" (type Validation).</t>
+        </is>
+      </c>
+      <c r="F146" s="22" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G146" s="22" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H146" s="22" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I146" s="22" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J146" s="22" t="inlineStr"/>
+      <c r="K146" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="24" t="inlineStr">
+        <is>
+          <t>M-407</t>
+        </is>
+      </c>
+      <c r="B147" s="24" t="inlineStr">
+        <is>
+          <t>Upload screens (Payment Uploads, BIR 2307, Commission ORs, B</t>
+        </is>
+      </c>
+      <c r="C147" s="24" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D147" s="24" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E147" s="24" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The basic commission must be above zero" (type Validation).</t>
+        </is>
+      </c>
+      <c r="F147" s="24" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G147" s="24" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H147" s="24" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I147" s="24" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J147" s="24" t="inlineStr"/>
+      <c r="K147" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="22" t="inlineStr">
+        <is>
+          <t>M-408</t>
+        </is>
+      </c>
+      <c r="B148" s="22" t="inlineStr">
+        <is>
+          <t>Every screen (Common screen elements)</t>
+        </is>
+      </c>
+      <c r="C148" s="22" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D148" s="22" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E148" s="22" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "You are not permitted to perform this action" (type Error).</t>
+        </is>
+      </c>
+      <c r="F148" s="22" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G148" s="22" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H148" s="22" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I148" s="22" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J148" s="22" t="inlineStr"/>
+      <c r="K148" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="24" t="inlineStr">
+        <is>
+          <t>M-409</t>
+        </is>
+      </c>
+      <c r="B149" s="24" t="inlineStr">
+        <is>
+          <t>Several screens</t>
+        </is>
+      </c>
+      <c r="C149" s="24" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D149" s="24" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E149" s="24" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the code and the name" (type Error).</t>
+        </is>
+      </c>
+      <c r="F149" s="24" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G149" s="24" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H149" s="24" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I149" s="24" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J149" s="24" t="inlineStr"/>
+      <c r="K149" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="22" t="inlineStr">
+        <is>
+          <t>M-410</t>
+        </is>
+      </c>
+      <c r="B150" s="22" t="inlineStr">
+        <is>
+          <t>Several screens</t>
+        </is>
+      </c>
+      <c r="C150" s="22" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D150" s="22" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E150" s="22" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Write each field as Field=position or Field=column, not '&lt;part&gt;'" (type Error).</t>
+        </is>
+      </c>
+      <c r="F150" s="22" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G150" s="22" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H150" s="22" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I150" s="22" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J150" s="22" t="inlineStr"/>
+      <c r="K150" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="24" t="inlineStr">
+        <is>
+          <t>M-411</t>
+        </is>
+      </c>
+      <c r="B151" s="24" t="inlineStr">
+        <is>
+          <t>Several screens</t>
+        </is>
+      </c>
+      <c r="C151" s="24" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D151" s="24" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E151" s="24" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The file cannot be read as an Excel workbook" (type Error).</t>
+        </is>
+      </c>
+      <c r="F151" s="24" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G151" s="24" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H151" s="24" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I151" s="24" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J151" s="24" t="inlineStr"/>
+      <c r="K151" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="22" t="inlineStr">
+        <is>
+          <t>M-412</t>
+        </is>
+      </c>
+      <c r="B152" s="22" t="inlineStr">
+        <is>
+          <t>Several screens</t>
+        </is>
+      </c>
+      <c r="C152" s="22" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D152" s="22" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E152" s="22" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The file name convention is not a valid pattern" (type Error).</t>
+        </is>
+      </c>
+      <c r="F152" s="22" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G152" s="22" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H152" s="22" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I152" s="22" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J152" s="22" t="inlineStr"/>
+      <c r="K152" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="24" t="inlineStr">
+        <is>
+          <t>M-413</t>
+        </is>
+      </c>
+      <c r="B153" s="24" t="inlineStr">
+        <is>
+          <t>Every screen (Common screen elements)</t>
+        </is>
+      </c>
+      <c r="C153" s="24" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D153" s="24" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E153" s="24" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The record was changed by another user. Please reload and try again." (type Error).</t>
+        </is>
+      </c>
+      <c r="F153" s="24" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G153" s="24" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H153" s="24" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I153" s="24" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J153" s="24" t="inlineStr"/>
+      <c r="K153" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="22" t="inlineStr">
+        <is>
+          <t>M-414</t>
+        </is>
+      </c>
+      <c r="B154" s="22" t="inlineStr">
+        <is>
+          <t>Several screens</t>
+        </is>
+      </c>
+      <c r="C154" s="22" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D154" s="22" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E154" s="22" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Version &lt;version no&gt; is not waiting for approval" (type Error).</t>
+        </is>
+      </c>
+      <c r="F154" s="22" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G154" s="22" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H154" s="22" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I154" s="22" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J154" s="22" t="inlineStr"/>
+      <c r="K154" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="24" t="inlineStr">
+        <is>
+          <t>M-415</t>
+        </is>
+      </c>
+      <c r="B155" s="24" t="inlineStr">
+        <is>
+          <t>Every screen (Common screen elements)</t>
+        </is>
+      </c>
+      <c r="C155" s="24" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D155" s="24" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E155" s="24" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The system could not complete the request. Try again; if it continues, contact support with the reference." (type Error).</t>
+        </is>
+      </c>
+      <c r="F155" s="24" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G155" s="24" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H155" s="24" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I155" s="24" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J155" s="24" t="inlineStr"/>
+      <c r="K155" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="22" t="inlineStr">
+        <is>
+          <t>M-416</t>
+        </is>
+      </c>
+      <c r="B156" s="22" t="inlineStr">
+        <is>
+          <t>Several screens</t>
+        </is>
+      </c>
+      <c r="C156" s="22" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D156" s="22" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E156" s="22" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The user who changed the form cannot approve it" (type Error).</t>
+        </is>
+      </c>
+      <c r="F156" s="22" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G156" s="22" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H156" s="22" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I156" s="22" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J156" s="22" t="inlineStr"/>
+      <c r="K156" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="24" t="inlineStr">
+        <is>
+          <t>M-417</t>
+        </is>
+      </c>
+      <c r="B157" s="24" t="inlineStr">
+        <is>
+          <t>Every screen (Common screen elements)</t>
+        </is>
+      </c>
+      <c r="C157" s="24" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D157" s="24" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E157" s="24" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Parameter '&lt;name&gt;' has an invalid value" (type Error).</t>
+        </is>
+      </c>
+      <c r="F157" s="24" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G157" s="24" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H157" s="24" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I157" s="24" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J157" s="24" t="inlineStr"/>
+      <c r="K157" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="22" t="inlineStr">
+        <is>
+          <t>M-418</t>
+        </is>
+      </c>
+      <c r="B158" s="22" t="inlineStr">
+        <is>
+          <t>Every screen (Common screen elements)</t>
+        </is>
+      </c>
+      <c r="C158" s="22" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D158" s="22" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E158" s="22" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Required parameter '&lt;parameter name&gt;' is missing" (type Error).</t>
+        </is>
+      </c>
+      <c r="F158" s="22" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G158" s="22" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H158" s="22" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I158" s="22" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J158" s="22" t="inlineStr"/>
+      <c r="K158" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="24" t="inlineStr">
+        <is>
+          <t>M-419</t>
+        </is>
+      </c>
+      <c r="B159" s="24" t="inlineStr">
+        <is>
+          <t>Several screens</t>
+        </is>
+      </c>
+      <c r="C159" s="24" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D159" s="24" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E159" s="24" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;name&gt; has no MFT folder" (type Error).</t>
+        </is>
+      </c>
+      <c r="F159" s="24" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G159" s="24" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H159" s="24" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I159" s="24" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J159" s="24" t="inlineStr"/>
+      <c r="K159" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="22" t="inlineStr">
+        <is>
+          <t>M-420</t>
+        </is>
+      </c>
+      <c r="B160" s="22" t="inlineStr">
+        <is>
+          <t>Several screens</t>
+        </is>
+      </c>
+      <c r="C160" s="22" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D160" s="22" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E160" s="22" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "An &lt;kind&gt; is issued when its creation record is posted: save it with Create &lt;kind&gt; and submit it for posting" (type Error).</t>
+        </is>
+      </c>
+      <c r="F160" s="22" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G160" s="22" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H160" s="22" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I160" s="22" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J160" s="22" t="inlineStr"/>
+      <c r="K160" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="24" t="inlineStr">
+        <is>
+          <t>M-421</t>
+        </is>
+      </c>
+      <c r="B161" s="24" t="inlineStr">
+        <is>
+          <t>Every screen (Common screen elements)</t>
+        </is>
+      </c>
+      <c r="C161" s="24" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D161" s="24" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E161" s="24" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The uploaded file is too large" (type Error).</t>
+        </is>
+      </c>
+      <c r="F161" s="24" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G161" s="24" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H161" s="24" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I161" s="24" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J161" s="24" t="inlineStr"/>
+      <c r="K161" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="22" t="inlineStr">
+        <is>
+          <t>M-422</t>
+        </is>
+      </c>
+      <c r="B162" s="22" t="inlineStr">
+        <is>
+          <t>Every screen (Common screen elements)</t>
+        </is>
+      </c>
+      <c r="C162" s="22" t="inlineStr">
+        <is>
+          <t>CSHID.001-025</t>
+        </is>
+      </c>
+      <c r="D162" s="22" t="inlineStr">
+        <is>
+          <t>Appendix F.2</t>
+        </is>
+      </c>
+      <c r="E162" s="22" t="inlineStr">
+        <is>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Invalid request" (type Error).</t>
+        </is>
+      </c>
+      <c r="F162" s="22" t="inlineStr">
+        <is>
+          <t>Confirm, or the new wording</t>
+        </is>
+      </c>
+      <c r="G162" s="22" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H162" s="22" t="inlineStr">
+        <is>
+          <t>Cashiering Process Owner</t>
+        </is>
+      </c>
+      <c r="I162" s="22" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J162" s="22" t="inlineStr"/>
+      <c r="K162" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A12:K144"/>
+  <autoFilter ref="A12:K162"/>
   <mergeCells count="5">
     <mergeCell ref="B4:K4"/>
     <mergeCell ref="B6:K6"/>
@@ -20637,7 +21591,7 @@
     <mergeCell ref="B5:K5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K14:K444" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="K14:K462" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_Inputs_BRD-02_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_Inputs_BRD-02_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>10 October 2026</t>
+          <t>11 October 2026</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_Inputs_BRD-02_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_Inputs_BRD-02_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Documents and print formats'!$12:$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'E-mail wordings'!$A$12:$K$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'E-mail wordings'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Messages to confirm'!$A$12:$K$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Messages to confirm'!$A$12:$K$144</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Messages to confirm'!$12:$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Schedules and timings'!$A$12:$K$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Schedules and timings'!$12:$12</definedName>
@@ -764,7 +764,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>BRD-02 Operations Cashiering - what the Business Unit provides for the FRS v3.2</t>
+          <t>BRD-02 Operations Cashiering - what the Business Unit provides for the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>149</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Master and reference data' the FRS v3.2 needs from the Business Unit.</t>
+          <t>Items of the kind 'Master and reference data' the FRS v3.3 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Approvers and users per role' the FRS v3.2 needs from the Business Unit.</t>
+          <t>Items of the kind 'Approvers and users per role' the FRS v3.3 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Integration inputs' the FRS v3.2 needs from the Business Unit.</t>
+          <t>Items of the kind 'Integration inputs' the FRS v3.3 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Open decisions' the FRS v3.2 needs from the Business Unit.</t>
+          <t>Items of the kind 'Open decisions' the FRS v3.3 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Any question or comment of the Business Unit on the items or on the FRS v3.2.</t>
+          <t>Any question or comment of the Business Unit on the items or on the FRS v3.3.</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr"/>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr"/>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr"/>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr"/>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr"/>
@@ -8375,7 +8375,7 @@
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr"/>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr"/>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="C116" s="14" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="D116" s="14" t="inlineStr"/>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>149 items</t>
+          <t>131 items</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="F7" s="22" t="n">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="G7" s="22">
         <f>COUNTIF('Messages to confirm'!K:K,"Open")</f>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Documents and print formats' the FRS v3.2 needs from the Business Unit.</t>
+          <t>Items of the kind 'Documents and print formats' the FRS v3.3 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'E-mail wordings' the FRS v3.2 needs from the Business Unit.</t>
+          <t>Items of the kind 'E-mail wordings' the FRS v3.3 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -13259,7 +13259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K162"/>
+  <dimension ref="A1:K144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Messages to confirm' the FRS v3.2 needs from the Business Unit.</t>
+          <t>Items of the kind 'Messages to confirm' the FRS v3.3 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -13531,7 +13531,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -14111,12 +14111,12 @@
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>M-049</t>
+          <t>M-020</t>
         </is>
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>AR and OR Forms and printing (SCR-OP-69, SCR-OP-18)</t>
+          <t>Receive Payment (SCR-OP-08) and the application of payments</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The effective date must be today or a later date" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A reclass or transfer moves the whole balance" (type Validation).</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -14164,12 +14164,12 @@
     <row r="23">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>M-050</t>
+          <t>M-021</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>AR and OR Forms and printing (SCR-OP-69, SCR-OP-18)</t>
+          <t>Receive Payment (SCR-OP-08) and the application of payments</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Select the AR form or the OR form" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Check number is required for a check payment" (type Validation).</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
@@ -14217,12 +14217,12 @@
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>M-051</t>
+          <t>M-022</t>
         </is>
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>AR and OR Forms and printing (SCR-OP-69, SCR-OP-18)</t>
+          <t>Receive Payment (SCR-OP-08) and the application of payments</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the reason for the rejection" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an ARN, invoice, policy or PN number to preview the application." (type Validation).</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -14270,7 +14270,7 @@
     <row r="25">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>M-053</t>
+          <t>M-023</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A reclass or transfer moves the whole balance" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero" (type Validation).</t>
         </is>
       </c>
       <c r="F25" s="24" t="inlineStr">
@@ -14323,7 +14323,7 @@
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>M-054</t>
+          <t>M-024</t>
         </is>
       </c>
       <c r="B26" s="22" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="E26" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Check number is required for a check payment" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero and at most &lt;balance&gt;" (type Validation).</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -14376,7 +14376,7 @@
     <row r="27">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>M-055</t>
+          <t>M-025</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an ARN, invoice, policy or PN number to preview the application." (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero and at most &lt;receipt amount&gt;" (type Validation).</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">
@@ -14429,7 +14429,7 @@
     <row r="28">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>M-056</t>
+          <t>M-026</t>
         </is>
       </c>
       <c r="B28" s="22" t="inlineStr">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter at least one reference, or the payor code for an unmatched payment" (type Validation).</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -14482,7 +14482,7 @@
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>M-057</t>
+          <t>M-027</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero and at most &lt;balance&gt;" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Payor name is required" (type Validation).</t>
         </is>
       </c>
       <c r="F29" s="24" t="inlineStr">
@@ -14535,7 +14535,7 @@
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>M-058</t>
+          <t>M-028</t>
         </is>
       </c>
       <c r="B30" s="22" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero and at most &lt;receipt amount&gt;" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Select a reason" (type Validation).</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -14588,7 +14588,7 @@
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>M-059</t>
+          <t>M-029</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="E31" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter at least one reference, or the payor code for an unmatched payment" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The reference belongs to a cancelled invoice: the payment goes to unapplied collections." (type Validation).</t>
         </is>
       </c>
       <c r="F31" s="24" t="inlineStr">
@@ -14641,7 +14641,7 @@
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
         <is>
-          <t>M-060</t>
+          <t>M-030</t>
         </is>
       </c>
       <c r="B32" s="22" t="inlineStr">
@@ -14661,7 +14661,7 @@
       </c>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Payor name is required" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Application &lt;id&gt; is already reversed" (type Error).</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -14694,7 +14694,7 @@
     <row r="33">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>M-061</t>
+          <t>M-031</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="E33" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Select a reason" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A non-premium AR needs the paying insurer's code" (type Error).</t>
         </is>
       </c>
       <c r="F33" s="24" t="inlineStr">
@@ -14747,7 +14747,7 @@
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>M-062</t>
+          <t>M-032</t>
         </is>
       </c>
       <c r="B34" s="22" t="inlineStr">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The reference belongs to a cancelled invoice: the payment goes to unapplied collections." (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Official receipts are issued by Head Office only" (type Error).</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -14800,7 +14800,7 @@
     <row r="35">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>M-063</t>
+          <t>M-033</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="E35" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Application &lt;id&gt; is already reversed" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "An official receipt needs a line" (type Error).</t>
         </is>
       </c>
       <c r="F35" s="24" t="inlineStr">
@@ -14853,7 +14853,7 @@
     <row r="36">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>M-064</t>
+          <t>M-034</t>
         </is>
       </c>
       <c r="B36" s="22" t="inlineStr">
@@ -14873,7 +14873,7 @@
       </c>
       <c r="E36" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A non-premium AR needs the paying insurer's code" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A receipt needs an amount above zero" (type Error).</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -14906,12 +14906,12 @@
     <row r="37">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>M-065</t>
+          <t>M-035</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>Receive Payment (SCR-OP-08) and the application of payments</t>
+          <t>Receipts, Issue Official Receipt and the receipt series (SCR</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="E37" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Official receipts are issued by Head Office only" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;receipt no&gt; issued" (type Confirmation).</t>
         </is>
       </c>
       <c r="F37" s="24" t="inlineStr">
@@ -14959,12 +14959,12 @@
     <row r="38">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>M-066</t>
+          <t>M-036</t>
         </is>
       </c>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>Receive Payment (SCR-OP-08) and the application of payments</t>
+          <t>Receipts, Issue Official Receipt and the receipt series (SCR</t>
         </is>
       </c>
       <c r="C38" s="22" t="inlineStr">
@@ -14979,7 +14979,7 @@
       </c>
       <c r="E38" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "An official receipt needs a line" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the gross amount" (type Validation).</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -15012,12 +15012,12 @@
     <row r="39">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>M-067</t>
+          <t>M-037</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>Receive Payment (SCR-OP-08) and the application of payments</t>
+          <t>Receipts, Issue Official Receipt and the receipt series (SCR</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="E39" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A receipt needs an amount above zero" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Payor name is required" (type Validation).</t>
         </is>
       </c>
       <c r="F39" s="24" t="inlineStr">
@@ -15065,7 +15065,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>M-068</t>
+          <t>M-038</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
@@ -15085,7 +15085,7 @@
       </c>
       <c r="E40" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;receipt no&gt; issued" (type Confirmation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Select the OR type" (type Validation).</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
@@ -15118,7 +15118,7 @@
     <row r="41">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>M-069</t>
+          <t>M-039</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="E41" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the gross amount" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "VAT and withholding tax cannot be negative" (type Validation).</t>
         </is>
       </c>
       <c r="F41" s="24" t="inlineStr">
@@ -15171,7 +15171,7 @@
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>M-070</t>
+          <t>M-040</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="E42" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No receipts match the search" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Branch &lt;code&gt; is not of this company" (type Error).</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
@@ -15224,7 +15224,7 @@
     <row r="43">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>M-071</t>
+          <t>M-041</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="E43" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Payor name is required" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The company has no Head Office branch for official receipts" (type Error).</t>
         </is>
       </c>
       <c r="F43" s="24" t="inlineStr">
@@ -15277,7 +15277,7 @@
     <row r="44">
       <c r="A44" s="22" t="inlineStr">
         <is>
-          <t>M-072</t>
+          <t>M-042</t>
         </is>
       </c>
       <c r="B44" s="22" t="inlineStr">
@@ -15297,7 +15297,7 @@
       </c>
       <c r="E44" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Select the OR type" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Official receipt series belong to Head Office only" (type Error).</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
@@ -15330,7 +15330,7 @@
     <row r="45">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>M-073</t>
+          <t>M-043</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="E45" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "VAT and withholding tax cannot be negative" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No authorized &lt;kind&gt; series with numbers left for this branch" (type Error).</t>
         </is>
       </c>
       <c r="F45" s="24" t="inlineStr">
@@ -15383,7 +15383,7 @@
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>M-074</t>
+          <t>M-044</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="E46" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Branch &lt;code&gt; is not of this company" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt series &lt;prefix&gt; is depleted" (type Error).</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
@@ -15436,7 +15436,7 @@
     <row r="47">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>M-075</t>
+          <t>M-045</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="E47" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The company has no Head Office branch for official receipts" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Next number &lt;legacy next no&gt; is outside &lt;from no&gt;-&lt;to no&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F47" s="24" t="inlineStr">
@@ -15489,7 +15489,7 @@
     <row r="48">
       <c r="A48" s="22" t="inlineStr">
         <is>
-          <t>M-076</t>
+          <t>M-046</t>
         </is>
       </c>
       <c r="B48" s="22" t="inlineStr">
@@ -15509,7 +15509,7 @@
       </c>
       <c r="E48" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Official receipt series belong to Head Office only" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The last number cannot be below the numbers already issued" (type Error).</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
@@ -15542,7 +15542,7 @@
     <row r="49">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>M-077</t>
+          <t>M-047</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No authorized &lt;kind&gt; series with numbers left for this branch" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The last number must not be below the first number" (type Error).</t>
         </is>
       </c>
       <c r="F49" s="24" t="inlineStr">
@@ -15595,12 +15595,12 @@
     <row r="50">
       <c r="A50" s="22" t="inlineStr">
         <is>
-          <t>M-078</t>
+          <t>M-048</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>Receipts, Issue Official Receipt and the receipt series (SCR</t>
+          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
         </is>
       </c>
       <c r="C50" s="22" t="inlineStr">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="E50" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt series &lt;prefix&gt; is depleted" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No cancellation or reinstatement" (type Information).</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
@@ -15648,12 +15648,12 @@
     <row r="51">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>M-079</t>
+          <t>M-049</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>Receipts, Issue Official Receipt and the receipt series (SCR</t>
+          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
@@ -15668,7 +15668,7 @@
       </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Next number &lt;legacy next no&gt; is outside &lt;from no&gt;-&lt;to no&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No items to display" (type Information).</t>
         </is>
       </c>
       <c r="F51" s="24" t="inlineStr">
@@ -15701,12 +15701,12 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>M-080</t>
+          <t>M-050</t>
         </is>
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>Receipts, Issue Official Receipt and the receipt series (SCR</t>
+          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
         </is>
       </c>
       <c r="C52" s="22" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="E52" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The last number cannot be below the numbers already issued" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No journal posted yet" (type Information).</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
@@ -15754,12 +15754,12 @@
     <row r="53">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>M-081</t>
+          <t>M-051</t>
         </is>
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>Receipts, Issue Official Receipt and the receipt series (SCR</t>
+          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
         </is>
       </c>
       <c r="C53" s="24" t="inlineStr">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="E53" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The last number must not be below the first number" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Nothing applied from this receipt" (type Information).</t>
         </is>
       </c>
       <c r="F53" s="24" t="inlineStr">
@@ -15807,12 +15807,12 @@
     <row r="54">
       <c r="A54" s="22" t="inlineStr">
         <is>
-          <t>M-082</t>
+          <t>M-052</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>Receipts, Issue Official Receipt and the receipt series (SCR</t>
+          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="E54" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The number format must hold the sequence {SEQ}" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The requested action is applied to the receipt." (type Validation).</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
@@ -15860,7 +15860,7 @@
     <row r="55">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>M-083</t>
+          <t>M-053</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="E55" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No cancellation or reinstatement" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The requester cannot approve &lt;transaction no&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F55" s="24" t="inlineStr">
@@ -15913,7 +15913,7 @@
     <row r="56">
       <c r="A56" s="22" t="inlineStr">
         <is>
-          <t>M-084</t>
+          <t>M-054</t>
         </is>
       </c>
       <c r="B56" s="22" t="inlineStr">
@@ -15933,7 +15933,7 @@
       </c>
       <c r="E56" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No items to display" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;transaction no&gt; is &lt;stage&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
@@ -15966,7 +15966,7 @@
     <row r="57">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>M-085</t>
+          <t>M-055</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="E57" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No journal posted yet" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt &lt;receipt no&gt; already has a request waiting for approval" (type Error).</t>
         </is>
       </c>
       <c r="F57" s="24" t="inlineStr">
@@ -16019,7 +16019,7 @@
     <row r="58">
       <c r="A58" s="22" t="inlineStr">
         <is>
-          <t>M-086</t>
+          <t>M-056</t>
         </is>
       </c>
       <c r="B58" s="22" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="E58" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Nothing applied from this receipt" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt &lt;receipt no&gt; is already cancelled" (type Error).</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
@@ -16072,7 +16072,7 @@
     <row r="59">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>M-087</t>
+          <t>M-057</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
@@ -16092,7 +16092,7 @@
       </c>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The requested action is applied to the receipt." (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Unapplied item &lt;reference&gt; of the receipt is &lt;stage&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F59" s="24" t="inlineStr">
@@ -16125,7 +16125,7 @@
     <row r="60">
       <c r="A60" s="22" t="inlineStr">
         <is>
-          <t>M-088</t>
+          <t>M-058</t>
         </is>
       </c>
       <c r="B60" s="22" t="inlineStr">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="E60" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The requester cannot approve &lt;transaction no&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Only a cancelled receipt can be reinstated" (type Error).</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
@@ -16178,7 +16178,7 @@
     <row r="61">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>M-089</t>
+          <t>M-059</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
@@ -16198,7 +16198,7 @@
       </c>
       <c r="E61" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;transaction no&gt; is &lt;stage&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Select a reason" (type Error).</t>
         </is>
       </c>
       <c r="F61" s="24" t="inlineStr">
@@ -16231,7 +16231,7 @@
     <row r="62">
       <c r="A62" s="22" t="inlineStr">
         <is>
-          <t>M-090</t>
+          <t>M-060</t>
         </is>
       </c>
       <c r="B62" s="22" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="E62" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt &lt;receipt no&gt; already has a request waiting for approval" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Specify the reason when 'Others' is selected" (type Error).</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
@@ -16284,7 +16284,7 @@
     <row r="63">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>M-091</t>
+          <t>M-061</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="E63" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt &lt;receipt no&gt; is already cancelled" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The reinstated amount must be above zero and at most &lt;amount&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F63" s="24" t="inlineStr">
@@ -16337,7 +16337,7 @@
     <row r="64">
       <c r="A64" s="22" t="inlineStr">
         <is>
-          <t>M-092</t>
+          <t>M-062</t>
         </is>
       </c>
       <c r="B64" s="22" t="inlineStr">
@@ -16357,7 +16357,7 @@
       </c>
       <c r="E64" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Unapplied item &lt;reference&gt; of the receipt is &lt;stage&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the &lt;missing&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
@@ -16390,7 +16390,7 @@
     <row r="65">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>M-093</t>
+          <t>M-063</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="E65" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Only a cancelled receipt can be reinstated" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Premium reinstatement reasons apply to ARs" (type Error).</t>
         </is>
       </c>
       <c r="F65" s="24" t="inlineStr">
@@ -16443,12 +16443,12 @@
     <row r="66">
       <c r="A66" s="22" t="inlineStr">
         <is>
-          <t>M-094</t>
+          <t>M-064</t>
         </is>
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
+          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
@@ -16463,7 +16463,7 @@
       </c>
       <c r="E66" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Select a reason" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Disposition updated" (type Confirmation).</t>
         </is>
       </c>
       <c r="F66" s="22" t="inlineStr">
@@ -16496,12 +16496,12 @@
     <row r="67">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>M-095</t>
+          <t>M-065</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
+          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
@@ -16516,7 +16516,7 @@
       </c>
       <c r="E67" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Specify the reason when 'Others' is selected" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No disposition yet" (type Information).</t>
         </is>
       </c>
       <c r="F67" s="24" t="inlineStr">
@@ -16549,12 +16549,12 @@
     <row r="68">
       <c r="A68" s="22" t="inlineStr">
         <is>
-          <t>M-096</t>
+          <t>M-066</t>
         </is>
       </c>
       <c r="B68" s="22" t="inlineStr">
         <is>
-          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
+          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
         </is>
       </c>
       <c r="C68" s="22" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="E68" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The reinstated amount must be above zero and at most &lt;amount&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The amount must be above zero and at most the balance &lt;balance&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
@@ -16602,12 +16602,12 @@
     <row r="69">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>M-097</t>
+          <t>M-067</t>
         </is>
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
+          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="E69" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the &lt;missing&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Invoice &lt;invoice no&gt; takes no client payment" (type Error).</t>
         </is>
       </c>
       <c r="F69" s="24" t="inlineStr">
@@ -16655,12 +16655,12 @@
     <row r="70">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>M-098</t>
+          <t>M-068</t>
         </is>
       </c>
       <c r="B70" s="22" t="inlineStr">
         <is>
-          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
+          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
         </is>
       </c>
       <c r="C70" s="22" t="inlineStr">
@@ -16675,7 +16675,7 @@
       </c>
       <c r="E70" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Premium reinstatement reasons apply to ARs" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown invoice &lt;invoice no&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F70" s="22" t="inlineStr">
@@ -16708,12 +16708,12 @@
     <row r="71">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>M-099</t>
+          <t>M-069</t>
         </is>
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>Receipt: cancellation and reinstatement (SCR-OP-10)</t>
+          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
         </is>
       </c>
       <c r="C71" s="24" t="inlineStr">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="E71" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Reinstatement of a cancelled receipt is not enabled (setting What Reinstate does)" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;description&gt; needs the team leader's approval and is not processed at once" (type Error).</t>
         </is>
       </c>
       <c r="F71" s="24" t="inlineStr">
@@ -16761,7 +16761,7 @@
     <row r="72">
       <c r="A72" s="22" t="inlineStr">
         <is>
-          <t>M-100</t>
+          <t>M-070</t>
         </is>
       </c>
       <c r="B72" s="22" t="inlineStr">
@@ -16781,7 +16781,7 @@
       </c>
       <c r="E72" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Disposition updated" (type Confirmation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Invoice &lt;target invoice no&gt; has nothing outstanding to apply to" (type Error).</t>
         </is>
       </c>
       <c r="F72" s="22" t="inlineStr">
@@ -16814,7 +16814,7 @@
     <row r="73">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>M-101</t>
+          <t>M-071</t>
         </is>
       </c>
       <c r="B73" s="24" t="inlineStr">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="E73" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No disposition yet" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No application" (type Error).</t>
         </is>
       </c>
       <c r="F73" s="24" t="inlineStr">
@@ -16867,7 +16867,7 @@
     <row r="74">
       <c r="A74" s="22" t="inlineStr">
         <is>
-          <t>M-102</t>
+          <t>M-072</t>
         </is>
       </c>
       <c r="B74" s="22" t="inlineStr">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="E74" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No unapplied payment matches the filters." (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter &lt;what&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F74" s="22" t="inlineStr">
@@ -16920,7 +16920,7 @@
     <row r="75">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>M-103</t>
+          <t>M-073</t>
         </is>
       </c>
       <c r="B75" s="24" t="inlineStr">
@@ -16940,7 +16940,7 @@
       </c>
       <c r="E75" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The amount must be above zero and at most the balance &lt;balance&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Disposition type &lt;type code&gt; has no processing rule" (type Error).</t>
         </is>
       </c>
       <c r="F75" s="24" t="inlineStr">
@@ -16973,7 +16973,7 @@
     <row r="76">
       <c r="A76" s="22" t="inlineStr">
         <is>
-          <t>M-104</t>
+          <t>M-074</t>
         </is>
       </c>
       <c r="B76" s="22" t="inlineStr">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="E76" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Invoice &lt;invoice no&gt; takes no client payment" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A reclass or transfer moves the whole balance &lt;balance&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F76" s="22" t="inlineStr">
@@ -17026,7 +17026,7 @@
     <row r="77">
       <c r="A77" s="24" t="inlineStr">
         <is>
-          <t>M-105</t>
+          <t>M-075</t>
         </is>
       </c>
       <c r="B77" s="24" t="inlineStr">
@@ -17046,7 +17046,7 @@
       </c>
       <c r="E77" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown invoice &lt;invoice no&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The requester cannot approve the disposition" (type Error).</t>
         </is>
       </c>
       <c r="F77" s="24" t="inlineStr">
@@ -17079,7 +17079,7 @@
     <row r="78">
       <c r="A78" s="22" t="inlineStr">
         <is>
-          <t>M-106</t>
+          <t>M-076</t>
         </is>
       </c>
       <c r="B78" s="22" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="E78" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;description&gt; needs the team leader's approval and is not processed at once" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A refund is reversed only after Disbursement returned the request" (type Error).</t>
         </is>
       </c>
       <c r="F78" s="22" t="inlineStr">
@@ -17132,7 +17132,7 @@
     <row r="79">
       <c r="A79" s="24" t="inlineStr">
         <is>
-          <t>M-107</t>
+          <t>M-077</t>
         </is>
       </c>
       <c r="B79" s="24" t="inlineStr">
@@ -17152,7 +17152,7 @@
       </c>
       <c r="E79" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Invoice &lt;target invoice no&gt; has nothing outstanding to apply to" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the reason for the reversal" (type Error).</t>
         </is>
       </c>
       <c r="F79" s="24" t="inlineStr">
@@ -17185,7 +17185,7 @@
     <row r="80">
       <c r="A80" s="22" t="inlineStr">
         <is>
-          <t>M-108</t>
+          <t>M-078</t>
         </is>
       </c>
       <c r="B80" s="22" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="E80" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No application" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "An unapplied item needs an amount above zero" (type Error).</t>
         </is>
       </c>
       <c r="F80" s="22" t="inlineStr">
@@ -17238,7 +17238,7 @@
     <row r="81">
       <c r="A81" s="24" t="inlineStr">
         <is>
-          <t>M-109</t>
+          <t>M-079</t>
         </is>
       </c>
       <c r="B81" s="24" t="inlineStr">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="E81" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter &lt;what&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Amount &lt;value&gt; is above the unapplied balance &lt;balance&gt; of &lt;reference&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F81" s="24" t="inlineStr">
@@ -17291,7 +17291,7 @@
     <row r="82">
       <c r="A82" s="22" t="inlineStr">
         <is>
-          <t>M-110</t>
+          <t>M-080</t>
         </is>
       </c>
       <c r="B82" s="22" t="inlineStr">
@@ -17311,7 +17311,7 @@
       </c>
       <c r="E82" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Disposition type &lt;type code&gt; has no processing rule" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;reference&gt; is &lt;stage&gt;, not &lt;stage&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F82" s="22" t="inlineStr">
@@ -17344,12 +17344,12 @@
     <row r="83">
       <c r="A83" s="24" t="inlineStr">
         <is>
-          <t>M-111</t>
+          <t>M-081</t>
         </is>
       </c>
       <c r="B83" s="24" t="inlineStr">
         <is>
-          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
+          <t>Incoming Requests (SCR-OP-13)</t>
         </is>
       </c>
       <c r="C83" s="24" t="inlineStr">
@@ -17364,7 +17364,7 @@
       </c>
       <c r="E83" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A reclass or transfer moves the whole balance &lt;balance&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero and at most the unapplied balance" (type Validation).</t>
         </is>
       </c>
       <c r="F83" s="24" t="inlineStr">
@@ -17397,12 +17397,12 @@
     <row r="84">
       <c r="A84" s="22" t="inlineStr">
         <is>
-          <t>M-112</t>
+          <t>M-082</t>
         </is>
       </c>
       <c r="B84" s="22" t="inlineStr">
         <is>
-          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
+          <t>Incoming Requests (SCR-OP-13)</t>
         </is>
       </c>
       <c r="C84" s="22" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="E84" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The requester cannot approve the disposition" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the client to reclass to" (type Validation).</t>
         </is>
       </c>
       <c r="F84" s="22" t="inlineStr">
@@ -17450,12 +17450,12 @@
     <row r="85">
       <c r="A85" s="24" t="inlineStr">
         <is>
-          <t>M-113</t>
+          <t>M-083</t>
         </is>
       </c>
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
+          <t>Incoming Requests (SCR-OP-13)</t>
         </is>
       </c>
       <c r="C85" s="24" t="inlineStr">
@@ -17470,7 +17470,7 @@
       </c>
       <c r="E85" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A refund is reversed only after Disbursement returned the request" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the marketing unit to transfer to" (type Validation).</t>
         </is>
       </c>
       <c r="F85" s="24" t="inlineStr">
@@ -17503,12 +17503,12 @@
     <row r="86">
       <c r="A86" s="22" t="inlineStr">
         <is>
-          <t>M-114</t>
+          <t>M-084</t>
         </is>
       </c>
       <c r="B86" s="22" t="inlineStr">
         <is>
-          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
+          <t>Incoming Requests (SCR-OP-13)</t>
         </is>
       </c>
       <c r="C86" s="22" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="E86" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the reason for the reversal" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No collector requests to display" (type Information).</t>
         </is>
       </c>
       <c r="F86" s="22" t="inlineStr">
@@ -17556,12 +17556,12 @@
     <row r="87">
       <c r="A87" s="24" t="inlineStr">
         <is>
-          <t>M-115</t>
+          <t>M-085</t>
         </is>
       </c>
       <c r="B87" s="24" t="inlineStr">
         <is>
-          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
+          <t>Incoming Requests (SCR-OP-13)</t>
         </is>
       </c>
       <c r="C87" s="24" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="E87" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "An unapplied item needs an amount above zero" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No payment reversals to display" (type Information).</t>
         </is>
       </c>
       <c r="F87" s="24" t="inlineStr">
@@ -17609,12 +17609,12 @@
     <row r="88">
       <c r="A88" s="22" t="inlineStr">
         <is>
-          <t>M-116</t>
+          <t>M-086</t>
         </is>
       </c>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
+          <t>Incoming Requests (SCR-OP-13)</t>
         </is>
       </c>
       <c r="C88" s="22" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="E88" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Amount &lt;value&gt; is above the unapplied balance &lt;balance&gt; of &lt;reference&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No refund validations to display" (type Information).</t>
         </is>
       </c>
       <c r="F88" s="22" t="inlineStr">
@@ -17662,12 +17662,12 @@
     <row r="89">
       <c r="A89" s="24" t="inlineStr">
         <is>
-          <t>M-117</t>
+          <t>M-087</t>
         </is>
       </c>
       <c r="B89" s="24" t="inlineStr">
         <is>
-          <t>Unapplied Payments and dispositions (SCR-OP-11, SCR-OP-12)</t>
+          <t>Incoming Requests (SCR-OP-13)</t>
         </is>
       </c>
       <c r="C89" s="24" t="inlineStr">
@@ -17682,7 +17682,7 @@
       </c>
       <c r="E89" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;reference&gt; is &lt;stage&gt;, not &lt;stage&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The selected receipt is reversed as requested." (type Validation).</t>
         </is>
       </c>
       <c r="F89" s="24" t="inlineStr">
@@ -17715,7 +17715,7 @@
     <row r="90">
       <c r="A90" s="22" t="inlineStr">
         <is>
-          <t>M-118</t>
+          <t>M-088</t>
         </is>
       </c>
       <c r="B90" s="22" t="inlineStr">
@@ -17735,7 +17735,7 @@
       </c>
       <c r="E90" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero and at most the unapplied balance" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;request no&gt; is already &lt;status&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
@@ -17768,7 +17768,7 @@
     <row r="91">
       <c r="A91" s="24" t="inlineStr">
         <is>
-          <t>M-119</t>
+          <t>M-089</t>
         </is>
       </c>
       <c r="B91" s="24" t="inlineStr">
@@ -17788,7 +17788,7 @@
       </c>
       <c r="E91" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the client to reclass to" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Disposition type &lt;type&gt; does not carry out a &lt;action&gt; request" (type Error).</t>
         </is>
       </c>
       <c r="F91" s="24" t="inlineStr">
@@ -17821,7 +17821,7 @@
     <row r="92">
       <c r="A92" s="22" t="inlineStr">
         <is>
-          <t>M-120</t>
+          <t>M-090</t>
         </is>
       </c>
       <c r="B92" s="22" t="inlineStr">
@@ -17841,7 +17841,7 @@
       </c>
       <c r="E92" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the marketing unit to transfer to" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown disposition type &lt;type&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F92" s="22" t="inlineStr">
@@ -17874,7 +17874,7 @@
     <row r="93">
       <c r="A93" s="24" t="inlineStr">
         <is>
-          <t>M-121</t>
+          <t>M-091</t>
         </is>
       </c>
       <c r="B93" s="24" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="E93" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No collector requests to display" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The requester cannot approve the payment reversal" (type Error).</t>
         </is>
       </c>
       <c r="F93" s="24" t="inlineStr">
@@ -17927,7 +17927,7 @@
     <row r="94">
       <c r="A94" s="22" t="inlineStr">
         <is>
-          <t>M-122</t>
+          <t>M-092</t>
         </is>
       </c>
       <c r="B94" s="22" t="inlineStr">
@@ -17947,7 +17947,7 @@
       </c>
       <c r="E94" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No payment reversals to display" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;request no&gt; is already &lt;status&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F94" s="22" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="95">
       <c r="A95" s="24" t="inlineStr">
         <is>
-          <t>M-123</t>
+          <t>M-093</t>
         </is>
       </c>
       <c r="B95" s="24" t="inlineStr">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="E95" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No refund validations to display" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt &lt;receipt no&gt; has &lt;available&gt; applied to &lt;invoice no&gt;, less than &lt;target&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F95" s="24" t="inlineStr">
@@ -18033,7 +18033,7 @@
     <row r="96">
       <c r="A96" s="22" t="inlineStr">
         <is>
-          <t>M-124</t>
+          <t>M-094</t>
         </is>
       </c>
       <c r="B96" s="22" t="inlineStr">
@@ -18053,7 +18053,7 @@
       </c>
       <c r="E96" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The selected receipt is reversed as requested." (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown receipt &lt;receipt no&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
@@ -18086,7 +18086,7 @@
     <row r="97">
       <c r="A97" s="24" t="inlineStr">
         <is>
-          <t>M-125</t>
+          <t>M-095</t>
         </is>
       </c>
       <c r="B97" s="24" t="inlineStr">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="E97" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;request no&gt; is already &lt;status&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;task no&gt; is already &lt;status&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F97" s="24" t="inlineStr">
@@ -18139,7 +18139,7 @@
     <row r="98">
       <c r="A98" s="22" t="inlineStr">
         <is>
-          <t>M-126</t>
+          <t>M-096</t>
         </is>
       </c>
       <c r="B98" s="22" t="inlineStr">
@@ -18159,7 +18159,7 @@
       </c>
       <c r="E98" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Disposition type &lt;type&gt; does not carry out a &lt;action&gt; request" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Choose the unapplied item that holds the returned premium" (type Error).</t>
         </is>
       </c>
       <c r="F98" s="22" t="inlineStr">
@@ -18192,7 +18192,7 @@
     <row r="99">
       <c r="A99" s="24" t="inlineStr">
         <is>
-          <t>M-127</t>
+          <t>M-097</t>
         </is>
       </c>
       <c r="B99" s="24" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="E99" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown disposition type &lt;type&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the reason for rejecting" (type Error).</t>
         </is>
       </c>
       <c r="F99" s="24" t="inlineStr">
@@ -18245,12 +18245,12 @@
     <row r="100">
       <c r="A100" s="22" t="inlineStr">
         <is>
-          <t>M-128</t>
+          <t>M-098</t>
         </is>
       </c>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>Incoming Requests (SCR-OP-13)</t>
+          <t>Pre-booked Payments (SCR-OP-14)</t>
         </is>
       </c>
       <c r="C100" s="22" t="inlineStr">
@@ -18265,7 +18265,7 @@
       </c>
       <c r="E100" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The requester cannot approve the payment reversal" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No items to display" (type Information).</t>
         </is>
       </c>
       <c r="F100" s="22" t="inlineStr">
@@ -18298,12 +18298,12 @@
     <row r="101">
       <c r="A101" s="24" t="inlineStr">
         <is>
-          <t>M-129</t>
+          <t>M-099</t>
         </is>
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>Incoming Requests (SCR-OP-13)</t>
+          <t>Pre-booked Payments (SCR-OP-14)</t>
         </is>
       </c>
       <c r="C101" s="24" t="inlineStr">
@@ -18318,7 +18318,7 @@
       </c>
       <c r="E101" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;request no&gt; is already &lt;status&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Pre-booked payment of &lt;arn&gt; is &lt;status&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F101" s="24" t="inlineStr">
@@ -18351,12 +18351,12 @@
     <row r="102">
       <c r="A102" s="22" t="inlineStr">
         <is>
-          <t>M-130</t>
+          <t>M-100</t>
         </is>
       </c>
       <c r="B102" s="22" t="inlineStr">
         <is>
-          <t>Incoming Requests (SCR-OP-13)</t>
+          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
         </is>
       </c>
       <c r="C102" s="22" t="inlineStr">
@@ -18371,7 +18371,7 @@
       </c>
       <c r="E102" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt &lt;receipt no&gt; has &lt;available&gt; applied to &lt;invoice no&gt;, less than &lt;target&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Layout of &lt;handler code&gt; saved" (type Confirmation).</t>
         </is>
       </c>
       <c r="F102" s="22" t="inlineStr">
@@ -18404,12 +18404,12 @@
     <row r="103">
       <c r="A103" s="24" t="inlineStr">
         <is>
-          <t>M-131</t>
+          <t>M-101</t>
         </is>
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>Incoming Requests (SCR-OP-13)</t>
+          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
         </is>
       </c>
       <c r="C103" s="24" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="E103" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown receipt &lt;receipt no&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No payment accepted in this run" (type Information).</t>
         </is>
       </c>
       <c r="F103" s="24" t="inlineStr">
@@ -18457,12 +18457,12 @@
     <row r="104">
       <c r="A104" s="22" t="inlineStr">
         <is>
-          <t>M-132</t>
+          <t>M-102</t>
         </is>
       </c>
       <c r="B104" s="22" t="inlineStr">
         <is>
-          <t>Incoming Requests (SCR-OP-13)</t>
+          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
         </is>
       </c>
       <c r="C104" s="22" t="inlineStr">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="E104" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;task no&gt; is already &lt;status&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Sweep done: &lt;premium&gt; premium balance(s) reversed, &lt;excess&gt; excess moved to overages" (type Confirmation).</t>
         </is>
       </c>
       <c r="F104" s="22" t="inlineStr">
@@ -18510,12 +18510,12 @@
     <row r="105">
       <c r="A105" s="24" t="inlineStr">
         <is>
-          <t>M-133</t>
+          <t>M-103</t>
         </is>
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>Incoming Requests (SCR-OP-13)</t>
+          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
         </is>
       </c>
       <c r="C105" s="24" t="inlineStr">
@@ -18530,7 +18530,7 @@
       </c>
       <c r="E105" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Choose the unapplied item that holds the returned premium" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A delimited layout needs a one-character separator" (type Error).</t>
         </is>
       </c>
       <c r="F105" s="24" t="inlineStr">
@@ -18563,12 +18563,12 @@
     <row r="106">
       <c r="A106" s="22" t="inlineStr">
         <is>
-          <t>M-134</t>
+          <t>M-104</t>
         </is>
       </c>
       <c r="B106" s="22" t="inlineStr">
         <is>
-          <t>Incoming Requests (SCR-OP-13)</t>
+          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
         </is>
       </c>
       <c r="C106" s="22" t="inlineStr">
@@ -18583,7 +18583,7 @@
       </c>
       <c r="E106" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the reason for rejecting" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A fixed-width layout needs its fields" (type Error).</t>
         </is>
       </c>
       <c r="F106" s="22" t="inlineStr">
@@ -18616,12 +18616,12 @@
     <row r="107">
       <c r="A107" s="24" t="inlineStr">
         <is>
-          <t>M-135</t>
+          <t>M-105</t>
         </is>
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>Pre-booked Payments (SCR-OP-14)</t>
+          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
         </is>
       </c>
       <c r="C107" s="24" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="E107" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No items to display" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Start and length of '&lt;part&gt;' must be numbers" (type Error).</t>
         </is>
       </c>
       <c r="F107" s="24" t="inlineStr">
@@ -18669,12 +18669,12 @@
     <row r="108">
       <c r="A108" s="22" t="inlineStr">
         <is>
-          <t>M-136</t>
+          <t>M-106</t>
         </is>
       </c>
       <c r="B108" s="22" t="inlineStr">
         <is>
-          <t>Pre-booked Payments (SCR-OP-14)</t>
+          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
         </is>
       </c>
       <c r="C108" s="22" t="inlineStr">
@@ -18689,7 +18689,7 @@
       </c>
       <c r="E108" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Pre-booked payment of &lt;arn&gt; is &lt;status&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Write each field as Header:start:length, not '&lt;part&gt;'" (type Error).</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
@@ -18722,7 +18722,7 @@
     <row r="109">
       <c r="A109" s="24" t="inlineStr">
         <is>
-          <t>M-137</t>
+          <t>M-107</t>
         </is>
       </c>
       <c r="B109" s="24" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="E109" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Layout of &lt;handler code&gt; saved" (type Confirmation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown layout kind &lt;new kind&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F109" s="24" t="inlineStr">
@@ -18775,12 +18775,12 @@
     <row r="110">
       <c r="A110" s="22" t="inlineStr">
         <is>
-          <t>M-138</t>
+          <t>M-108</t>
         </is>
       </c>
       <c r="B110" s="22" t="inlineStr">
         <is>
-          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
+          <t>PDC Warehouse (SCR-OP-16)</t>
         </is>
       </c>
       <c r="C110" s="22" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="E110" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No payment accepted in this run" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero" (type Validation).</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
@@ -18828,12 +18828,12 @@
     <row r="111">
       <c r="A111" s="24" t="inlineStr">
         <is>
-          <t>M-139</t>
+          <t>M-109</t>
         </is>
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
+          <t>PDC Warehouse (SCR-OP-16)</t>
         </is>
       </c>
       <c r="C111" s="24" t="inlineStr">
@@ -18848,7 +18848,7 @@
       </c>
       <c r="E111" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Sweep done: &lt;premium&gt; reversed, &lt;excess&gt; excess moved to overages" (type Confirmation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "PDC warehouse updated" (type Confirmation).</t>
         </is>
       </c>
       <c r="F111" s="24" t="inlineStr">
@@ -18881,12 +18881,12 @@
     <row r="112">
       <c r="A112" s="22" t="inlineStr">
         <is>
-          <t>M-140</t>
+          <t>M-110</t>
         </is>
       </c>
       <c r="B112" s="22" t="inlineStr">
         <is>
-          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
+          <t>PDC Warehouse (SCR-OP-16)</t>
         </is>
       </c>
       <c r="C112" s="22" t="inlineStr">
@@ -18901,7 +18901,7 @@
       </c>
       <c r="E112" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A delimited layout needs a one-character separator" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A post-dated check needs an amount above zero" (type Error).</t>
         </is>
       </c>
       <c r="F112" s="22" t="inlineStr">
@@ -18934,12 +18934,12 @@
     <row r="113">
       <c r="A113" s="24" t="inlineStr">
         <is>
-          <t>M-141</t>
+          <t>M-111</t>
         </is>
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
+          <t>PDC Warehouse (SCR-OP-16)</t>
         </is>
       </c>
       <c r="C113" s="24" t="inlineStr">
@@ -18954,7 +18954,7 @@
       </c>
       <c r="E113" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A fixed-width layout needs its fields" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Check &lt;bank code&gt; &lt;check no&gt; is already warehoused" (type Error).</t>
         </is>
       </c>
       <c r="F113" s="24" t="inlineStr">
@@ -18987,12 +18987,12 @@
     <row r="114">
       <c r="A114" s="22" t="inlineStr">
         <is>
-          <t>M-142</t>
+          <t>M-112</t>
         </is>
       </c>
       <c r="B114" s="22" t="inlineStr">
         <is>
-          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
+          <t>PDC Warehouse (SCR-OP-16)</t>
         </is>
       </c>
       <c r="C114" s="22" t="inlineStr">
@@ -19007,7 +19007,7 @@
       </c>
       <c r="E114" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Start and length of '&lt;part&gt;' must be numbers" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Check &lt;warehouse no&gt; is &lt;status&gt;, not in the warehouse" (type Error).</t>
         </is>
       </c>
       <c r="F114" s="22" t="inlineStr">
@@ -19040,12 +19040,12 @@
     <row r="115">
       <c r="A115" s="24" t="inlineStr">
         <is>
-          <t>M-143</t>
+          <t>M-113</t>
         </is>
       </c>
       <c r="B115" s="24" t="inlineStr">
         <is>
-          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
+          <t>PDC Warehouse (SCR-OP-16)</t>
         </is>
       </c>
       <c r="C115" s="24" t="inlineStr">
@@ -19060,7 +19060,7 @@
       </c>
       <c r="E115" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Write each field as Header:start:length, not '&lt;part&gt;'" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "A check leaves the warehouse as returned, replaced or pulled out" (type Error).</t>
         </is>
       </c>
       <c r="F115" s="24" t="inlineStr">
@@ -19093,12 +19093,12 @@
     <row r="116">
       <c r="A116" s="22" t="inlineStr">
         <is>
-          <t>M-144</t>
+          <t>M-114</t>
         </is>
       </c>
       <c r="B116" s="22" t="inlineStr">
         <is>
-          <t>Payment Uploads and Cashiering Setup (SCR-OP-15, SCR-OP-22)</t>
+          <t>Batch Print (SCR-OP-18)</t>
         </is>
       </c>
       <c r="C116" s="22" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="E116" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown layout kind &lt;new kind&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;batch no&gt;: &lt;printed count&gt; printed, &lt;failed count&gt; failed" (type Confirmation).</t>
         </is>
       </c>
       <c r="F116" s="22" t="inlineStr">
@@ -19146,12 +19146,12 @@
     <row r="117">
       <c r="A117" s="24" t="inlineStr">
         <is>
-          <t>M-145</t>
+          <t>M-115</t>
         </is>
       </c>
       <c r="B117" s="24" t="inlineStr">
         <is>
-          <t>PDC Warehouse (SCR-OP-16)</t>
+          <t>Batch Print (SCR-OP-18)</t>
         </is>
       </c>
       <c r="C117" s="24" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="E117" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter an amount above zero" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No print batch yet" (type Information).</t>
         </is>
       </c>
       <c r="F117" s="24" t="inlineStr">
@@ -19199,12 +19199,12 @@
     <row r="118">
       <c r="A118" s="22" t="inlineStr">
         <is>
-          <t>M-146</t>
+          <t>M-116</t>
         </is>
       </c>
       <c r="B118" s="22" t="inlineStr">
         <is>
-          <t>PDC Warehouse (SCR-OP-16)</t>
+          <t>Batch Print (SCR-OP-18)</t>
         </is>
       </c>
       <c r="C118" s="22" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="E118" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No post-dated checks" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No receipts match the criteria" (type Information).</t>
         </is>
       </c>
       <c r="F118" s="22" t="inlineStr">
@@ -19252,12 +19252,12 @@
     <row r="119">
       <c r="A119" s="24" t="inlineStr">
         <is>
-          <t>M-147</t>
+          <t>M-117</t>
         </is>
       </c>
       <c r="B119" s="24" t="inlineStr">
         <is>
-          <t>PDC Warehouse (SCR-OP-16)</t>
+          <t>Batch Print (SCR-OP-18)</t>
         </is>
       </c>
       <c r="C119" s="24" t="inlineStr">
@@ -19272,7 +19272,7 @@
       </c>
       <c r="E119" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "PDC warehouse updated" (type Confirmation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt &lt;receipt no&gt; is cancelled" (type Error).</t>
         </is>
       </c>
       <c r="F119" s="24" t="inlineStr">
@@ -19305,12 +19305,12 @@
     <row r="120">
       <c r="A120" s="22" t="inlineStr">
         <is>
-          <t>M-148</t>
+          <t>M-118</t>
         </is>
       </c>
       <c r="B120" s="22" t="inlineStr">
         <is>
-          <t>PDC Warehouse (SCR-OP-16)</t>
+          <t>Batch Print (SCR-OP-18)</t>
         </is>
       </c>
       <c r="C120" s="22" t="inlineStr">
@@ -19325,7 +19325,7 @@
       </c>
       <c r="E120" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A post-dated check needs an amount above zero" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;batch no&gt; has no failures" (type Error).</t>
         </is>
       </c>
       <c r="F120" s="22" t="inlineStr">
@@ -19358,12 +19358,12 @@
     <row r="121">
       <c r="A121" s="24" t="inlineStr">
         <is>
-          <t>M-149</t>
+          <t>M-119</t>
         </is>
       </c>
       <c r="B121" s="24" t="inlineStr">
         <is>
-          <t>PDC Warehouse (SCR-OP-16)</t>
+          <t>Batch Print (SCR-OP-18)</t>
         </is>
       </c>
       <c r="C121" s="24" t="inlineStr">
@@ -19378,7 +19378,7 @@
       </c>
       <c r="E121" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Check &lt;bank code&gt; &lt;check no&gt; is already warehoused" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Select between 1 and 500 receipts to print" (type Error).</t>
         </is>
       </c>
       <c r="F121" s="24" t="inlineStr">
@@ -19411,12 +19411,12 @@
     <row r="122">
       <c r="A122" s="22" t="inlineStr">
         <is>
-          <t>M-150</t>
+          <t>M-140</t>
         </is>
       </c>
       <c r="B122" s="22" t="inlineStr">
         <is>
-          <t>PDC Warehouse (SCR-OP-16)</t>
+          <t>Commission ORs (SCR-OP-20)</t>
         </is>
       </c>
       <c r="C122" s="22" t="inlineStr">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="E122" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Check &lt;warehouse no&gt; is &lt;status&gt;, not in the warehouse" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No commission payment waiting for an OR" (type Information).</t>
         </is>
       </c>
       <c r="F122" s="22" t="inlineStr">
@@ -19464,12 +19464,12 @@
     <row r="123">
       <c r="A123" s="24" t="inlineStr">
         <is>
-          <t>M-151</t>
+          <t>M-141</t>
         </is>
       </c>
       <c r="B123" s="24" t="inlineStr">
         <is>
-          <t>PDC Warehouse (SCR-OP-16)</t>
+          <t>Commission ORs (SCR-OP-20)</t>
         </is>
       </c>
       <c r="C123" s="24" t="inlineStr">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="E123" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "A check leaves the warehouse as returned, replaced or pulled out" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown company &lt;company&gt;" (type Error).</t>
         </is>
       </c>
       <c r="F123" s="24" t="inlineStr">
@@ -19517,12 +19517,12 @@
     <row r="124">
       <c r="A124" s="22" t="inlineStr">
         <is>
-          <t>M-152</t>
+          <t>M-351</t>
         </is>
       </c>
       <c r="B124" s="22" t="inlineStr">
         <is>
-          <t>Batch Print (SCR-OP-18)</t>
+          <t>Interfaces (SCR-OP-61)</t>
         </is>
       </c>
       <c r="C124" s="22" t="inlineStr">
@@ -19537,7 +19537,7 @@
       </c>
       <c r="E124" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;batch no&gt;: &lt;printed count&gt; printed, &lt;failed count&gt; not printed" (type Confirmation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;name&gt; saved" (type Confirmation).</t>
         </is>
       </c>
       <c r="F124" s="22" t="inlineStr">
@@ -19570,12 +19570,12 @@
     <row r="125">
       <c r="A125" s="24" t="inlineStr">
         <is>
-          <t>M-153</t>
+          <t>M-352</t>
         </is>
       </c>
       <c r="B125" s="24" t="inlineStr">
         <is>
-          <t>Batch Print (SCR-OP-18)</t>
+          <t>Interfaces (SCR-OP-61)</t>
         </is>
       </c>
       <c r="C125" s="24" t="inlineStr">
@@ -19590,7 +19590,7 @@
       </c>
       <c r="E125" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Receipt &lt;receipt no&gt; is cancelled" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No records in this run" (type Information).</t>
         </is>
       </c>
       <c r="F125" s="24" t="inlineStr">
@@ -19623,12 +19623,12 @@
     <row r="126">
       <c r="A126" s="22" t="inlineStr">
         <is>
-          <t>M-154</t>
+          <t>M-353</t>
         </is>
       </c>
       <c r="B126" s="22" t="inlineStr">
         <is>
-          <t>Batch Print (SCR-OP-18)</t>
+          <t>Interfaces (SCR-OP-61)</t>
         </is>
       </c>
       <c r="C126" s="22" t="inlineStr">
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E126" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;batch no&gt; has no failure to skip" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No runs yet" (type Information).</t>
         </is>
       </c>
       <c r="F126" s="22" t="inlineStr">
@@ -19676,12 +19676,12 @@
     <row r="127">
       <c r="A127" s="24" t="inlineStr">
         <is>
-          <t>M-155</t>
+          <t>M-354</t>
         </is>
       </c>
       <c r="B127" s="24" t="inlineStr">
         <is>
-          <t>Batch Print (SCR-OP-18)</t>
+          <t>Interfaces (SCR-OP-61)</t>
         </is>
       </c>
       <c r="C127" s="24" t="inlineStr">
@@ -19696,7 +19696,7 @@
       </c>
       <c r="E127" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;batch no&gt; has no failures" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Feed &lt;code&gt; is inactive" (type Error).</t>
         </is>
       </c>
       <c r="F127" s="24" t="inlineStr">
@@ -19729,12 +19729,12 @@
     <row r="128">
       <c r="A128" s="22" t="inlineStr">
         <is>
-          <t>M-156</t>
+          <t>M-355</t>
         </is>
       </c>
       <c r="B128" s="22" t="inlineStr">
         <is>
-          <t>Batch Print (SCR-OP-18)</t>
+          <t>Interfaces (SCR-OP-61)</t>
         </is>
       </c>
       <c r="C128" s="22" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E128" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;batch no&gt; has no ZIP of its receipts" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No module processes uploads of feed &lt;feed code&gt; yet" (type Error).</t>
         </is>
       </c>
       <c r="F128" s="22" t="inlineStr">
@@ -19782,12 +19782,12 @@
     <row r="129">
       <c r="A129" s="24" t="inlineStr">
         <is>
-          <t>M-157</t>
+          <t>M-356</t>
         </is>
       </c>
       <c r="B129" s="24" t="inlineStr">
         <is>
-          <t>Batch Print (SCR-OP-18)</t>
+          <t>Several screens</t>
         </is>
       </c>
       <c r="C129" s="24" t="inlineStr">
@@ -19802,7 +19802,7 @@
       </c>
       <c r="E129" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Select between 1 and 500 receipts to print" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "No receipt series yet" (type Information).</t>
         </is>
       </c>
       <c r="F129" s="24" t="inlineStr">
@@ -19835,12 +19835,12 @@
     <row r="130">
       <c r="A130" s="22" t="inlineStr">
         <is>
-          <t>M-178</t>
+          <t>M-357</t>
         </is>
       </c>
       <c r="B130" s="22" t="inlineStr">
         <is>
-          <t>Commission ORs (SCR-OP-20)</t>
+          <t>Several screens</t>
         </is>
       </c>
       <c r="C130" s="22" t="inlineStr">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="E130" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No commission payment waiting for an OR" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Prefix is required" (type Validation).</t>
         </is>
       </c>
       <c r="F130" s="22" t="inlineStr">
@@ -19888,12 +19888,12 @@
     <row r="131">
       <c r="A131" s="24" t="inlineStr">
         <is>
-          <t>M-179</t>
+          <t>M-358</t>
         </is>
       </c>
       <c r="B131" s="24" t="inlineStr">
         <is>
-          <t>Commission ORs (SCR-OP-20)</t>
+          <t>Several screens</t>
         </is>
       </c>
       <c r="C131" s="24" t="inlineStr">
@@ -19908,7 +19908,7 @@
       </c>
       <c r="E131" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Unknown company &lt;company&gt;" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Series &lt;prefix&gt; saved" (type Confirmation).</t>
         </is>
       </c>
       <c r="F131" s="24" t="inlineStr">
@@ -19941,12 +19941,12 @@
     <row r="132">
       <c r="A132" s="22" t="inlineStr">
         <is>
-          <t>M-389</t>
+          <t>M-359</t>
         </is>
       </c>
       <c r="B132" s="22" t="inlineStr">
         <is>
-          <t>Interfaces (SCR-OP-61)</t>
+          <t>Several screens</t>
         </is>
       </c>
       <c r="C132" s="22" t="inlineStr">
@@ -19961,7 +19961,7 @@
       </c>
       <c r="E132" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;name&gt; saved" (type Confirmation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The range must end at or after its start" (type Validation).</t>
         </is>
       </c>
       <c r="F132" s="22" t="inlineStr">
@@ -19994,12 +19994,12 @@
     <row r="133">
       <c r="A133" s="24" t="inlineStr">
         <is>
-          <t>M-390</t>
+          <t>M-360</t>
         </is>
       </c>
       <c r="B133" s="24" t="inlineStr">
         <is>
-          <t>Interfaces (SCR-OP-61)</t>
+          <t>Several screens</t>
         </is>
       </c>
       <c r="C133" s="24" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="E133" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No records in this run" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The series becomes active for issuing receipts." (type Validation).</t>
         </is>
       </c>
       <c r="F133" s="24" t="inlineStr">
@@ -20047,12 +20047,12 @@
     <row r="134">
       <c r="A134" s="22" t="inlineStr">
         <is>
-          <t>M-391</t>
+          <t>M-361</t>
         </is>
       </c>
       <c r="B134" s="22" t="inlineStr">
         <is>
-          <t>Interfaces (SCR-OP-61)</t>
+          <t>Upload screens (Payment Uploads, BIR 2307, Commission ORs, B</t>
         </is>
       </c>
       <c r="C134" s="22" t="inlineStr">
@@ -20067,7 +20067,7 @@
       </c>
       <c r="E134" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No runs yet" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;" (type Validation).</t>
         </is>
       </c>
       <c r="F134" s="22" t="inlineStr">
@@ -20100,12 +20100,12 @@
     <row r="135">
       <c r="A135" s="24" t="inlineStr">
         <is>
-          <t>M-392</t>
+          <t>M-362</t>
         </is>
       </c>
       <c r="B135" s="24" t="inlineStr">
         <is>
-          <t>Interfaces (SCR-OP-61)</t>
+          <t>Upload screens (Payment Uploads, BIR 2307, Commission ORs, B</t>
         </is>
       </c>
       <c r="C135" s="24" t="inlineStr">
@@ -20120,7 +20120,7 @@
       </c>
       <c r="E135" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Feed &lt;code&gt; is inactive" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;Column&gt; is mandatory" (type Validation).</t>
         </is>
       </c>
       <c r="F135" s="24" t="inlineStr">
@@ -20153,12 +20153,12 @@
     <row r="136">
       <c r="A136" s="22" t="inlineStr">
         <is>
-          <t>M-393</t>
+          <t>M-366</t>
         </is>
       </c>
       <c r="B136" s="22" t="inlineStr">
         <is>
-          <t>Interfaces (SCR-OP-61)</t>
+          <t>Upload screens (Payment Uploads, BIR 2307, Commission ORs, B</t>
         </is>
       </c>
       <c r="C136" s="22" t="inlineStr">
@@ -20173,7 +20173,7 @@
       </c>
       <c r="E136" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No module processes uploads of feed &lt;feed code&gt; yet" (type Error).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The amount must be above zero" (type Validation).</t>
         </is>
       </c>
       <c r="F136" s="22" t="inlineStr">
@@ -20206,12 +20206,12 @@
     <row r="137">
       <c r="A137" s="24" t="inlineStr">
         <is>
-          <t>M-394</t>
+          <t>M-367</t>
         </is>
       </c>
       <c r="B137" s="24" t="inlineStr">
         <is>
-          <t>Several screens</t>
+          <t>Upload screens (Payment Uploads, BIR 2307, Commission ORs, B</t>
         </is>
       </c>
       <c r="C137" s="24" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="E137" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "No receipt series yet" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The basic commission must be above zero" (type Validation).</t>
         </is>
       </c>
       <c r="F137" s="24" t="inlineStr">
@@ -20259,12 +20259,12 @@
     <row r="138">
       <c r="A138" s="22" t="inlineStr">
         <is>
-          <t>M-395</t>
+          <t>M-368</t>
         </is>
       </c>
       <c r="B138" s="22" t="inlineStr">
         <is>
-          <t>Several screens</t>
+          <t>Every screen (Common screen elements)</t>
         </is>
       </c>
       <c r="C138" s="22" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="E138" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Nothing to show" (type Information).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "You are not permitted to perform this action" (type Error).</t>
         </is>
       </c>
       <c r="F138" s="22" t="inlineStr">
@@ -20312,12 +20312,12 @@
     <row r="139">
       <c r="A139" s="24" t="inlineStr">
         <is>
-          <t>M-396</t>
+          <t>M-369</t>
         </is>
       </c>
       <c r="B139" s="24" t="inlineStr">
         <is>
-          <t>Several screens</t>
+          <t>Every screen (Common screen elements)</t>
         </is>
       </c>
       <c r="C139" s="24" t="inlineStr">
@@ -20332,7 +20332,7 @@
       </c>
       <c r="E139" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Prefix is required" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The record was changed by another user. Please reload and try again." (type Error).</t>
         </is>
       </c>
       <c r="F139" s="24" t="inlineStr">
@@ -20365,12 +20365,12 @@
     <row r="140">
       <c r="A140" s="22" t="inlineStr">
         <is>
-          <t>M-397</t>
+          <t>M-370</t>
         </is>
       </c>
       <c r="B140" s="22" t="inlineStr">
         <is>
-          <t>Several screens</t>
+          <t>Every screen (Common screen elements)</t>
         </is>
       </c>
       <c r="C140" s="22" t="inlineStr">
@@ -20385,7 +20385,7 @@
       </c>
       <c r="E140" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Series &lt;prefix&gt; saved" (type Confirmation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The system could not complete the request. Try again; if it continues, contact support with the reference." (type Error).</t>
         </is>
       </c>
       <c r="F140" s="22" t="inlineStr">
@@ -20418,12 +20418,12 @@
     <row r="141">
       <c r="A141" s="24" t="inlineStr">
         <is>
-          <t>M-398</t>
+          <t>M-371</t>
         </is>
       </c>
       <c r="B141" s="24" t="inlineStr">
         <is>
-          <t>Several screens</t>
+          <t>Every screen (Common screen elements)</t>
         </is>
       </c>
       <c r="C141" s="24" t="inlineStr">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="E141" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The number format must hold the sequence {SEQ}" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Parameter '&lt;name&gt;' has an invalid value" (type Error).</t>
         </is>
       </c>
       <c r="F141" s="24" t="inlineStr">
@@ -20471,12 +20471,12 @@
     <row r="142">
       <c r="A142" s="22" t="inlineStr">
         <is>
-          <t>M-399</t>
+          <t>M-372</t>
         </is>
       </c>
       <c r="B142" s="22" t="inlineStr">
         <is>
-          <t>Several screens</t>
+          <t>Every screen (Common screen elements)</t>
         </is>
       </c>
       <c r="C142" s="22" t="inlineStr">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="E142" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The range must end at or after its start" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Required parameter '&lt;parameter name&gt;' is missing" (type Error).</t>
         </is>
       </c>
       <c r="F142" s="22" t="inlineStr">
@@ -20524,12 +20524,12 @@
     <row r="143">
       <c r="A143" s="24" t="inlineStr">
         <is>
-          <t>M-400</t>
+          <t>M-373</t>
         </is>
       </c>
       <c r="B143" s="24" t="inlineStr">
         <is>
-          <t>Several screens</t>
+          <t>Every screen (Common screen elements)</t>
         </is>
       </c>
       <c r="C143" s="24" t="inlineStr">
@@ -20544,7 +20544,7 @@
       </c>
       <c r="E143" s="24" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The series becomes active for issuing receipts." (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "The uploaded file is too large" (type Error).</t>
         </is>
       </c>
       <c r="F143" s="24" t="inlineStr">
@@ -20577,12 +20577,12 @@
     <row r="144">
       <c r="A144" s="22" t="inlineStr">
         <is>
-          <t>M-401</t>
+          <t>M-374</t>
         </is>
       </c>
       <c r="B144" s="22" t="inlineStr">
         <is>
-          <t>Upload screens (Payment Uploads, BIR 2307, Commission ORs, B</t>
+          <t>Every screen (Common screen elements)</t>
         </is>
       </c>
       <c r="C144" s="22" t="inlineStr">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="E144" s="22" t="inlineStr">
         <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;" (type Validation).</t>
+          <t>Confirm the wording of the message, or give BDOI's wording: "Invalid request" (type Error).</t>
         </is>
       </c>
       <c r="F144" s="22" t="inlineStr">
@@ -20627,962 +20627,8 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="24" t="inlineStr">
-        <is>
-          <t>M-402</t>
-        </is>
-      </c>
-      <c r="B145" s="24" t="inlineStr">
-        <is>
-          <t>Upload screens (Payment Uploads, BIR 2307, Commission ORs, B</t>
-        </is>
-      </c>
-      <c r="C145" s="24" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D145" s="24" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E145" s="24" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;Column&gt; is mandatory" (type Validation).</t>
-        </is>
-      </c>
-      <c r="F145" s="24" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G145" s="24" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H145" s="24" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I145" s="24" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J145" s="24" t="inlineStr"/>
-      <c r="K145" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="22" t="inlineStr">
-        <is>
-          <t>M-406</t>
-        </is>
-      </c>
-      <c r="B146" s="22" t="inlineStr">
-        <is>
-          <t>Upload screens (Payment Uploads, BIR 2307, Commission ORs, B</t>
-        </is>
-      </c>
-      <c r="C146" s="22" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D146" s="22" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E146" s="22" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The amount must be above zero" (type Validation).</t>
-        </is>
-      </c>
-      <c r="F146" s="22" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G146" s="22" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H146" s="22" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I146" s="22" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J146" s="22" t="inlineStr"/>
-      <c r="K146" s="22" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="24" t="inlineStr">
-        <is>
-          <t>M-407</t>
-        </is>
-      </c>
-      <c r="B147" s="24" t="inlineStr">
-        <is>
-          <t>Upload screens (Payment Uploads, BIR 2307, Commission ORs, B</t>
-        </is>
-      </c>
-      <c r="C147" s="24" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D147" s="24" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E147" s="24" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The basic commission must be above zero" (type Validation).</t>
-        </is>
-      </c>
-      <c r="F147" s="24" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G147" s="24" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H147" s="24" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I147" s="24" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J147" s="24" t="inlineStr"/>
-      <c r="K147" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="22" t="inlineStr">
-        <is>
-          <t>M-408</t>
-        </is>
-      </c>
-      <c r="B148" s="22" t="inlineStr">
-        <is>
-          <t>Every screen (Common screen elements)</t>
-        </is>
-      </c>
-      <c r="C148" s="22" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D148" s="22" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E148" s="22" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "You are not permitted to perform this action" (type Error).</t>
-        </is>
-      </c>
-      <c r="F148" s="22" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G148" s="22" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H148" s="22" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I148" s="22" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J148" s="22" t="inlineStr"/>
-      <c r="K148" s="22" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="24" t="inlineStr">
-        <is>
-          <t>M-409</t>
-        </is>
-      </c>
-      <c r="B149" s="24" t="inlineStr">
-        <is>
-          <t>Several screens</t>
-        </is>
-      </c>
-      <c r="C149" s="24" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D149" s="24" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E149" s="24" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Enter the code and the name" (type Error).</t>
-        </is>
-      </c>
-      <c r="F149" s="24" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G149" s="24" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H149" s="24" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I149" s="24" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J149" s="24" t="inlineStr"/>
-      <c r="K149" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="22" t="inlineStr">
-        <is>
-          <t>M-410</t>
-        </is>
-      </c>
-      <c r="B150" s="22" t="inlineStr">
-        <is>
-          <t>Several screens</t>
-        </is>
-      </c>
-      <c r="C150" s="22" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D150" s="22" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E150" s="22" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Write each field as Field=position or Field=column, not '&lt;part&gt;'" (type Error).</t>
-        </is>
-      </c>
-      <c r="F150" s="22" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G150" s="22" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H150" s="22" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I150" s="22" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J150" s="22" t="inlineStr"/>
-      <c r="K150" s="22" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="24" t="inlineStr">
-        <is>
-          <t>M-411</t>
-        </is>
-      </c>
-      <c r="B151" s="24" t="inlineStr">
-        <is>
-          <t>Several screens</t>
-        </is>
-      </c>
-      <c r="C151" s="24" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D151" s="24" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E151" s="24" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The file cannot be read as an Excel workbook" (type Error).</t>
-        </is>
-      </c>
-      <c r="F151" s="24" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G151" s="24" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H151" s="24" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I151" s="24" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J151" s="24" t="inlineStr"/>
-      <c r="K151" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="22" t="inlineStr">
-        <is>
-          <t>M-412</t>
-        </is>
-      </c>
-      <c r="B152" s="22" t="inlineStr">
-        <is>
-          <t>Several screens</t>
-        </is>
-      </c>
-      <c r="C152" s="22" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D152" s="22" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E152" s="22" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The file name convention is not a valid pattern" (type Error).</t>
-        </is>
-      </c>
-      <c r="F152" s="22" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G152" s="22" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H152" s="22" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I152" s="22" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J152" s="22" t="inlineStr"/>
-      <c r="K152" s="22" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="24" t="inlineStr">
-        <is>
-          <t>M-413</t>
-        </is>
-      </c>
-      <c r="B153" s="24" t="inlineStr">
-        <is>
-          <t>Every screen (Common screen elements)</t>
-        </is>
-      </c>
-      <c r="C153" s="24" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D153" s="24" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E153" s="24" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The record was changed by another user. Please reload and try again." (type Error).</t>
-        </is>
-      </c>
-      <c r="F153" s="24" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G153" s="24" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H153" s="24" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I153" s="24" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J153" s="24" t="inlineStr"/>
-      <c r="K153" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="22" t="inlineStr">
-        <is>
-          <t>M-414</t>
-        </is>
-      </c>
-      <c r="B154" s="22" t="inlineStr">
-        <is>
-          <t>Several screens</t>
-        </is>
-      </c>
-      <c r="C154" s="22" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D154" s="22" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E154" s="22" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Version &lt;version no&gt; is not waiting for approval" (type Error).</t>
-        </is>
-      </c>
-      <c r="F154" s="22" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G154" s="22" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H154" s="22" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I154" s="22" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J154" s="22" t="inlineStr"/>
-      <c r="K154" s="22" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="24" t="inlineStr">
-        <is>
-          <t>M-415</t>
-        </is>
-      </c>
-      <c r="B155" s="24" t="inlineStr">
-        <is>
-          <t>Every screen (Common screen elements)</t>
-        </is>
-      </c>
-      <c r="C155" s="24" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D155" s="24" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E155" s="24" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The system could not complete the request. Try again; if it continues, contact support with the reference." (type Error).</t>
-        </is>
-      </c>
-      <c r="F155" s="24" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G155" s="24" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H155" s="24" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I155" s="24" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J155" s="24" t="inlineStr"/>
-      <c r="K155" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="22" t="inlineStr">
-        <is>
-          <t>M-416</t>
-        </is>
-      </c>
-      <c r="B156" s="22" t="inlineStr">
-        <is>
-          <t>Several screens</t>
-        </is>
-      </c>
-      <c r="C156" s="22" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D156" s="22" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E156" s="22" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The user who changed the form cannot approve it" (type Error).</t>
-        </is>
-      </c>
-      <c r="F156" s="22" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G156" s="22" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H156" s="22" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I156" s="22" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J156" s="22" t="inlineStr"/>
-      <c r="K156" s="22" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="24" t="inlineStr">
-        <is>
-          <t>M-417</t>
-        </is>
-      </c>
-      <c r="B157" s="24" t="inlineStr">
-        <is>
-          <t>Every screen (Common screen elements)</t>
-        </is>
-      </c>
-      <c r="C157" s="24" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D157" s="24" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E157" s="24" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Parameter '&lt;name&gt;' has an invalid value" (type Error).</t>
-        </is>
-      </c>
-      <c r="F157" s="24" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G157" s="24" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H157" s="24" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I157" s="24" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J157" s="24" t="inlineStr"/>
-      <c r="K157" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="22" t="inlineStr">
-        <is>
-          <t>M-418</t>
-        </is>
-      </c>
-      <c r="B158" s="22" t="inlineStr">
-        <is>
-          <t>Every screen (Common screen elements)</t>
-        </is>
-      </c>
-      <c r="C158" s="22" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D158" s="22" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E158" s="22" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Required parameter '&lt;parameter name&gt;' is missing" (type Error).</t>
-        </is>
-      </c>
-      <c r="F158" s="22" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G158" s="22" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H158" s="22" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I158" s="22" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J158" s="22" t="inlineStr"/>
-      <c r="K158" s="22" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="24" t="inlineStr">
-        <is>
-          <t>M-419</t>
-        </is>
-      </c>
-      <c r="B159" s="24" t="inlineStr">
-        <is>
-          <t>Several screens</t>
-        </is>
-      </c>
-      <c r="C159" s="24" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D159" s="24" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E159" s="24" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "&lt;name&gt; has no MFT folder" (type Error).</t>
-        </is>
-      </c>
-      <c r="F159" s="24" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G159" s="24" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H159" s="24" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I159" s="24" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J159" s="24" t="inlineStr"/>
-      <c r="K159" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="22" t="inlineStr">
-        <is>
-          <t>M-420</t>
-        </is>
-      </c>
-      <c r="B160" s="22" t="inlineStr">
-        <is>
-          <t>Several screens</t>
-        </is>
-      </c>
-      <c r="C160" s="22" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D160" s="22" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E160" s="22" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "An &lt;kind&gt; is issued when its creation record is posted: save it with Create &lt;kind&gt; and submit it for posting" (type Error).</t>
-        </is>
-      </c>
-      <c r="F160" s="22" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G160" s="22" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H160" s="22" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I160" s="22" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J160" s="22" t="inlineStr"/>
-      <c r="K160" s="22" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="24" t="inlineStr">
-        <is>
-          <t>M-421</t>
-        </is>
-      </c>
-      <c r="B161" s="24" t="inlineStr">
-        <is>
-          <t>Every screen (Common screen elements)</t>
-        </is>
-      </c>
-      <c r="C161" s="24" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D161" s="24" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E161" s="24" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "The uploaded file is too large" (type Error).</t>
-        </is>
-      </c>
-      <c r="F161" s="24" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G161" s="24" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H161" s="24" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I161" s="24" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J161" s="24" t="inlineStr"/>
-      <c r="K161" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="22" t="inlineStr">
-        <is>
-          <t>M-422</t>
-        </is>
-      </c>
-      <c r="B162" s="22" t="inlineStr">
-        <is>
-          <t>Every screen (Common screen elements)</t>
-        </is>
-      </c>
-      <c r="C162" s="22" t="inlineStr">
-        <is>
-          <t>CSHID.001-025</t>
-        </is>
-      </c>
-      <c r="D162" s="22" t="inlineStr">
-        <is>
-          <t>Appendix F.2</t>
-        </is>
-      </c>
-      <c r="E162" s="22" t="inlineStr">
-        <is>
-          <t>Confirm the wording of the message, or give BDOI's wording: "Invalid request" (type Error).</t>
-        </is>
-      </c>
-      <c r="F162" s="22" t="inlineStr">
-        <is>
-          <t>Confirm, or the new wording</t>
-        </is>
-      </c>
-      <c r="G162" s="22" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H162" s="22" t="inlineStr">
-        <is>
-          <t>Cashiering Process Owner</t>
-        </is>
-      </c>
-      <c r="I162" s="22" t="inlineStr">
-        <is>
-          <t>16-Jul-2027</t>
-        </is>
-      </c>
-      <c r="J162" s="22" t="inlineStr"/>
-      <c r="K162" s="22" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A12:K162"/>
+  <autoFilter ref="A12:K144"/>
   <mergeCells count="5">
     <mergeCell ref="B4:K4"/>
     <mergeCell ref="B6:K6"/>
@@ -21591,7 +20637,7 @@
     <mergeCell ref="B5:K5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K14:K462" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="K14:K444" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -21646,7 +20692,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Schedules and timings' the FRS v3.2 needs from the Business Unit.</t>
+          <t>Items of the kind 'Schedules and timings' the FRS v3.3 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -21887,7 +20933,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -22741,7 +21787,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Parameters and thresholds' the FRS v3.2 needs from the Business Unit.</t>
+          <t>Items of the kind 'Parameters and thresholds' the FRS v3.3 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -22982,7 +22028,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -23783,7 +22829,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Lists of values' the FRS v3.2 needs from the Business Unit.</t>
+          <t>Items of the kind 'Lists of values' the FRS v3.3 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -24024,7 +23070,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or appendix of the FRS v3.2</t>
+          <t>FR item or appendix of the FRS v3.3</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_Inputs_BRD-02_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_Inputs_BRD-02_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E36"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -740,13 +740,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -775,6 +778,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -847,6 +851,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -1064,6 +1069,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="B34" s="15" t="inlineStr">
         <is>
@@ -1071,6 +1077,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36" ht="26" customHeight="1">
       <c r="B36" s="16" t="inlineStr">
         <is>
@@ -1198,6 +1205,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -2558,6 +2566,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -3812,6 +3821,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -4120,7 +4130,7 @@
       </c>
       <c r="E13" s="30" t="inlineStr">
         <is>
-          <t>MFT folder, arrival time, positions 7 to 13 of the layout (exchanged: Bills Payment file BDOIYYYYMMDD.txt with its header record (Appendix D.1); Daily, via MFT, taken at the times set and on Receive MFT Files Now). Status of BDOI's input: Given in part (sample, file name). Available in BIBS: intake with the name, size, duplicate and header checks, run report, refusal alert and processing again; run end to end in SIT and UAT against the channel simulator. Connection details from BDOI IT at SIT.</t>
+          <t>MFT folder, arrival time, positions 7 to 13 of the layout (exchanged: Bills Payment file BDOIYYYYMMDD.txt with its header record (Appendix D.1); Daily, via MFT, taken at the times set and on Receive MFT Files Now). Status of BDOI's input: Given in part (sample, file name). Proposed: intake with the name, size, duplicate and header checks, run report, refusal alert and processing again. Connection details from BDOI IT at SIT.</t>
         </is>
       </c>
       <c r="F13" s="30" t="inlineStr">
@@ -4177,7 +4187,7 @@
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>MFT folder, arrival time, positions 7 to 13 of the layout (exchanged: Bills Payment file BDOIYYYYMMDD.txt with its header record (Appendix D.1); Daily, via MFT, taken at the times set and on Receive MFT Files Now). Status of BDOI's input: Given in part (sample, file name). Available in BIBS: intake with the name, size, duplicate and header checks, run report, refusal alert and processing again; run end to end in SIT and UAT against the channel simulator. Connection details from BDOI IT at SIT.</t>
+          <t>MFT folder, arrival time, positions 7 to 13 of the layout (exchanged: Bills Payment file BDOIYYYYMMDD.txt with its header record (Appendix D.1); Daily, via MFT, taken at the times set and on Receive MFT Files Now). Status of BDOI's input: Given in part (sample, file name). Proposed: intake with the name, size, duplicate and header checks, run report, refusal alert and processing again. Connection details from BDOI IT at SIT.</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -4230,7 +4240,7 @@
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>MFT folder, time, the header and detail layout (exchanged: Matured post-dated checks BDOIYYYYMMDDPMS.txt (Appendix D.2); Daily, via MFT). Status of BDOI's input: To be provided. Available in BIBS in the proposed layout and run end to end against the channel simulator; layout and folder from BDOI IT at SIT.</t>
+          <t>MFT folder, time, the header and detail layout (exchanged: Matured post-dated checks BDOIYYYYMMDDPMS.txt (Appendix D.2); Daily, via MFT). Status of BDOI's input: To be provided. Proposed layout (Appendix D); layout and folder from BDOI IT at SIT.</t>
         </is>
       </c>
       <c r="F15" s="24" t="inlineStr">
@@ -4283,7 +4293,7 @@
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>Separator of the file (exchanged: Trade file UploadTrade_MM.DD.YYYY.txt (Appendix D.4); Daily, upload by the Cashier (several files in one upload)). Status of BDOI's input: Given in part (sample). Available in BIBS; the channel simulator writes the file for SIT and UAT.</t>
+          <t>Separator of the file (exchanged: Trade file UploadTrade_MM.DD.YYYY.txt (Appendix D.4); Daily, upload by the Cashier (several files in one upload)). Status of BDOI's input: Given in part (sample).</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -4336,7 +4346,7 @@
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>Layout of the file (exchanged: Direct Credit file OTCYYYYMMDD-&lt;branch&gt;.txt (Appendix D.5) identifying the payments of a Bills Payment file (setting, Appendix H.8); Daily, upload). Status of BDOI's input: To be provided. Available in BIBS in the proposed layout; the channel simulator writes the file for SIT and UAT.</t>
+          <t>Layout of the file (exchanged: Direct Credit file OTCYYYYMMDD-&lt;branch&gt;.txt (Appendix D.5) identifying the payments of a Bills Payment file (setting, Appendix H.8); Daily, upload). Status of BDOI's input: To be provided. Proposed layout (Appendix D).</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">
@@ -4389,7 +4399,7 @@
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>- (exchanged: CLPC file CLPC-MonDDYYYY.xlsx with its TOTAL row (Appendix D.3); Daily, upload). Status of BDOI's input: Given (sample). Available in BIBS; the channel simulator writes the file for SIT and UAT.</t>
+          <t>- (exchanged: CLPC file CLPC-MonDDYYYY.xlsx with its TOTAL row (Appendix D.3); Daily, upload). Status of BDOI's input: Given (sample).</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -4442,7 +4452,7 @@
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>- (exchanged: Commission Schedule of the commission paid by an insurer, matched to the commission receivable of each account; At each insurer payment, upload). Status of BDOI's input: Layout proposed in BIBS (Appendix D); valid lines processed as delivered (setting, Appendix H.8).</t>
+          <t>- (exchanged: Commission Schedule of the commission paid by an insurer, matched to the commission receivable of each account; At each insurer payment, upload). Status of BDOI's input: Layout proposed (Appendix D); valid lines processed by default (setting, Appendix H.8).</t>
         </is>
       </c>
       <c r="F19" s="24" t="inlineStr">
@@ -4480,7 +4490,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>Channel simulator (SIT and UAT only)</t>
+          <t>Test files of the payment channels (SIT and UAT)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -5458,6 +5468,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -6399,6 +6410,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -6746,6 +6758,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -9094,6 +9107,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -9721,6 +9735,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -11876,6 +11891,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -12824,7 +12840,7 @@
       </c>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>Approve the wording, the trigger and the recipients. Trigger: A Pre-booked payment waits for the booking of its account beyond the ageing threshold (5 days as delivered). Recipients: Cashiering Team Leader (alert inbox). Subject: Payment for &lt;ARN&gt; waits for the booking since &lt;date&gt;. Text: The pre-booked payment and its amount.</t>
+          <t>Approve the wording, the trigger and the recipients. Trigger: A Pre-booked payment waits for the booking of its account beyond the ageing threshold (5 days by default). Recipients: Cashiering Team Leader (alert inbox). Subject: Payment for &lt;ARN&gt; waits for the booking since &lt;date&gt;. Text: The pre-booked payment and its amount.</t>
         </is>
       </c>
       <c r="F25" s="24" t="inlineStr">
@@ -13342,6 +13358,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -20744,6 +20761,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -21839,6 +21857,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -22881,6 +22900,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_Inputs_BRD-02_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_Inputs_BRD-02_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -26,6 +26,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$130</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Start here'!$A$4:$I$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Start here'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Documents and print formats'!$A$12:$K$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Documents and print formats'!$12:$12</definedName>
@@ -1105,7 +1106,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2467,7 +2468,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3722,7 +3723,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -5369,7 +5370,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -6315,7 +6316,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -6643,7 +6644,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -6719,7 +6720,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -9063,7 +9064,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -9611,6 +9612,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:I15"/>
   <mergeCells count="1">
     <mergeCell ref="A2:I2"/>
   </mergeCells>
@@ -9636,7 +9638,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -11792,7 +11794,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -13259,7 +13261,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -20662,7 +20664,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -21758,7 +21760,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -22801,7 +22803,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -24109,7 +24111,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
